--- a/website/assets/files/FY2015_Dataset.xlsx
+++ b/website/assets/files/FY2015_Dataset.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11003"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fowlkes_d\Work Folders\Documents\PaymentAccuracy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeffhawley/source/omb-payment-accuracy/website/assets/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E28883-A909-254B-B4F4-80DBDF5BC674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6840" tabRatio="782" firstSheet="4" activeTab="9"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="32800" windowHeight="17060" tabRatio="782" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agency Results" sheetId="16" r:id="rId1"/>
@@ -54,10 +55,21 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Root Cause table'!$A:$C,'Root Cause table'!$3:$3</definedName>
     <definedName name="programs">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1704,7 +1716,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="15">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
@@ -1722,7 +1734,7 @@
     <numFmt numFmtId="173" formatCode="#,##0.000"/>
     <numFmt numFmtId="174" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="48" x14ac:knownFonts="1">
+  <fonts count="48">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3918,37 +3930,37 @@
     </xf>
   </cellXfs>
   <cellStyles count="31">
-    <cellStyle name="Comma 2" xfId="5"/>
-    <cellStyle name="Comma 2 2" xfId="24"/>
-    <cellStyle name="Comma 2 2 2" xfId="29"/>
+    <cellStyle name="Comma 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Comma 2 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Comma 2 2 2" xfId="29" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Currency" xfId="20" builtinId="4"/>
-    <cellStyle name="Currency 2" xfId="4"/>
-    <cellStyle name="Currency 2 2" xfId="25"/>
-    <cellStyle name="Currency 3" xfId="8"/>
-    <cellStyle name="Currency 4" xfId="19"/>
-    <cellStyle name="Currency 5" xfId="16"/>
+    <cellStyle name="Currency 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Currency 2 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Currency 3" xfId="8" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Currency 4" xfId="19" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Currency 5" xfId="16" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="15"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 2 2" xfId="3"/>
-    <cellStyle name="Normal 2 2 2" xfId="10"/>
-    <cellStyle name="Normal 2 3" xfId="14"/>
-    <cellStyle name="Normal 2 3 2" xfId="30"/>
-    <cellStyle name="Normal 2 4" xfId="23"/>
-    <cellStyle name="Normal 2 4 2" xfId="28"/>
-    <cellStyle name="Normal 2_Sheet1" xfId="21"/>
-    <cellStyle name="Normal 3" xfId="6"/>
-    <cellStyle name="Normal 3 2" xfId="9"/>
-    <cellStyle name="Normal 4" xfId="13"/>
-    <cellStyle name="Normal 4 2" xfId="27"/>
-    <cellStyle name="Normal 5" xfId="11"/>
-    <cellStyle name="Normal 6" xfId="22"/>
-    <cellStyle name="Normal 9" xfId="18"/>
+    <cellStyle name="Normal 10" xfId="15" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal 2 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Normal 2 3" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Normal 2 3 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Normal 2 4" xfId="23" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Normal 2 4 2" xfId="28" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Normal 2_Sheet1" xfId="21" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Normal 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Normal 3 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Normal 4" xfId="13" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Normal 4 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Normal 5" xfId="11" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Normal 6" xfId="22" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Normal 9" xfId="18" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
-    <cellStyle name="Percent 2" xfId="7"/>
-    <cellStyle name="Percent 2 2" xfId="12"/>
-    <cellStyle name="Percent 2 2 2" xfId="26"/>
-    <cellStyle name="Percent 4" xfId="17"/>
+    <cellStyle name="Percent 2" xfId="7" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="Percent 2 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Percent 2 2 2" xfId="26" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Percent 4" xfId="17" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4230,43 +4242,43 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX36"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="11.65" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="10.53125" style="44" customWidth="1"/>
-    <col min="2" max="2" width="15.46484375" style="43" customWidth="1"/>
-    <col min="3" max="4" width="11.86328125" style="43" customWidth="1"/>
-    <col min="5" max="5" width="16.1328125" style="43" customWidth="1"/>
-    <col min="6" max="7" width="11.86328125" style="43" customWidth="1"/>
-    <col min="8" max="8" width="13.53125" style="43" customWidth="1"/>
-    <col min="9" max="10" width="11.86328125" style="43" customWidth="1"/>
-    <col min="11" max="11" width="13.53125" style="43" customWidth="1"/>
-    <col min="12" max="25" width="11.86328125" style="43" customWidth="1"/>
-    <col min="26" max="26" width="14.46484375" style="43" customWidth="1"/>
-    <col min="27" max="28" width="11.86328125" style="43" customWidth="1"/>
-    <col min="29" max="29" width="14.86328125" style="44" customWidth="1"/>
-    <col min="30" max="31" width="11.86328125" style="44" customWidth="1"/>
-    <col min="32" max="32" width="13.46484375" style="44" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="44" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="43" customWidth="1"/>
+    <col min="3" max="4" width="11.83203125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="16.1640625" style="43" customWidth="1"/>
+    <col min="6" max="7" width="11.83203125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="13.5" style="43" customWidth="1"/>
+    <col min="9" max="10" width="11.83203125" style="43" customWidth="1"/>
+    <col min="11" max="11" width="13.5" style="43" customWidth="1"/>
+    <col min="12" max="25" width="11.83203125" style="43" customWidth="1"/>
+    <col min="26" max="26" width="14.5" style="43" customWidth="1"/>
+    <col min="27" max="28" width="11.83203125" style="43" customWidth="1"/>
+    <col min="29" max="29" width="14.83203125" style="44" customWidth="1"/>
+    <col min="30" max="31" width="11.83203125" style="44" customWidth="1"/>
+    <col min="32" max="32" width="13.5" style="44" customWidth="1"/>
     <col min="33" max="33" width="12" style="44" customWidth="1"/>
-    <col min="34" max="34" width="9.53125" style="44" customWidth="1"/>
-    <col min="35" max="35" width="13.1328125" style="44" customWidth="1"/>
-    <col min="36" max="36" width="11.86328125" style="44" customWidth="1"/>
-    <col min="37" max="37" width="9.1328125" style="44"/>
-    <col min="38" max="38" width="9.86328125" style="48" customWidth="1"/>
-    <col min="39" max="39" width="16.46484375" style="44" customWidth="1"/>
-    <col min="40" max="40" width="12.46484375" style="49" customWidth="1"/>
-    <col min="41" max="41" width="9.53125" style="44" customWidth="1"/>
-    <col min="42" max="42" width="13.86328125" style="49" customWidth="1"/>
-    <col min="43" max="43" width="11.1328125" style="49" customWidth="1"/>
-    <col min="44" max="44" width="8.53125" style="44" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="14.53125" style="44" customWidth="1"/>
-    <col min="46" max="46" width="12.53125" style="49" customWidth="1"/>
+    <col min="34" max="34" width="9.5" style="44" customWidth="1"/>
+    <col min="35" max="35" width="13.1640625" style="44" customWidth="1"/>
+    <col min="36" max="36" width="11.83203125" style="44" customWidth="1"/>
+    <col min="37" max="37" width="9.1640625" style="44"/>
+    <col min="38" max="38" width="9.83203125" style="48" customWidth="1"/>
+    <col min="39" max="39" width="16.5" style="44" customWidth="1"/>
+    <col min="40" max="40" width="12.5" style="49" customWidth="1"/>
+    <col min="41" max="41" width="9.5" style="44" customWidth="1"/>
+    <col min="42" max="42" width="13.83203125" style="49" customWidth="1"/>
+    <col min="43" max="43" width="11.1640625" style="49" customWidth="1"/>
+    <col min="44" max="44" width="8.5" style="44" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="14.5" style="44" customWidth="1"/>
+    <col min="46" max="46" width="12.5" style="49" customWidth="1"/>
     <col min="47" max="47" width="10" style="48" customWidth="1"/>
-    <col min="48" max="16384" width="9.1328125" style="44"/>
+    <col min="48" max="16384" width="9.1640625" style="44"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:49" ht="26.25" customHeight="1" thickBot="1">
       <c r="A1" s="190"/>
       <c r="B1" s="361" t="s">
         <v>167</v>
@@ -4345,7 +4357,7 @@
       <c r="AT1" s="362"/>
       <c r="AU1" s="363"/>
     </row>
-    <row r="2" spans="1:49" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:49" ht="18.75" customHeight="1" thickBot="1">
       <c r="A2" s="190"/>
       <c r="B2" s="165" t="s">
         <v>4</v>
@@ -4484,7 +4496,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:49" s="45" customFormat="1" ht="27" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:49" s="45" customFormat="1" ht="27" customHeight="1" thickTop="1" thickBot="1">
       <c r="A3" s="190"/>
       <c r="B3" s="191">
         <v>1035354.15</v>
@@ -4623,7 +4635,7 @@
         <v>3.7567899509035468E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:49" s="45" customFormat="1" ht="35.65" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:49" s="45" customFormat="1" ht="41" thickTop="1" thickBot="1">
       <c r="A4" s="51" t="s">
         <v>7</v>
       </c>
@@ -4768,7 +4780,7 @@
       <c r="AV4" s="47"/>
       <c r="AW4" s="47"/>
     </row>
-    <row r="5" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A5" s="32" t="s">
         <v>260</v>
       </c>
@@ -4821,7 +4833,7 @@
       <c r="AV5" s="46"/>
       <c r="AW5" s="46"/>
     </row>
-    <row r="6" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A6" s="32" t="s">
         <v>20</v>
       </c>
@@ -4911,7 +4923,7 @@
       <c r="AV6" s="46"/>
       <c r="AW6" s="46"/>
     </row>
-    <row r="7" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A7" s="33" t="s">
         <v>22</v>
       </c>
@@ -5049,7 +5061,7 @@
       <c r="AV7" s="46"/>
       <c r="AW7" s="46"/>
     </row>
-    <row r="8" spans="1:49" s="45" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:49" s="45" customFormat="1" ht="13">
       <c r="A8" s="33" t="s">
         <v>23</v>
       </c>
@@ -5139,7 +5151,7 @@
       <c r="AV8" s="46"/>
       <c r="AW8" s="46"/>
     </row>
-    <row r="9" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A9" s="33" t="s">
         <v>24</v>
       </c>
@@ -5289,7 +5301,7 @@
       <c r="AV9" s="46"/>
       <c r="AW9" s="46"/>
     </row>
-    <row r="10" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A10" s="209" t="s">
         <v>27</v>
       </c>
@@ -5372,7 +5384,7 @@
       <c r="AV10" s="46"/>
       <c r="AW10" s="46"/>
     </row>
-    <row r="11" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A11" s="33" t="s">
         <v>29</v>
       </c>
@@ -5467,7 +5479,7 @@
       <c r="AV11" s="46"/>
       <c r="AW11" s="46"/>
     </row>
-    <row r="12" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A12" s="33" t="s">
         <v>31</v>
       </c>
@@ -5617,7 +5629,7 @@
       <c r="AV12" s="46"/>
       <c r="AW12" s="46"/>
     </row>
-    <row r="13" spans="1:49" s="45" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:49" s="45" customFormat="1">
       <c r="A13" s="211" t="s">
         <v>33</v>
       </c>
@@ -5755,7 +5767,7 @@
       <c r="AV13" s="46"/>
       <c r="AW13" s="46"/>
     </row>
-    <row r="14" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A14" s="33" t="s">
         <v>42</v>
       </c>
@@ -5905,7 +5917,7 @@
       <c r="AV14" s="46"/>
       <c r="AW14" s="46"/>
     </row>
-    <row r="15" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A15" s="33" t="s">
         <v>45</v>
       </c>
@@ -6055,7 +6067,7 @@
       <c r="AV15" s="46"/>
       <c r="AW15" s="46"/>
     </row>
-    <row r="16" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:49" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A16" s="33" t="s">
         <v>49</v>
       </c>
@@ -6175,7 +6187,7 @@
       <c r="AV16" s="46"/>
       <c r="AW16" s="46"/>
     </row>
-    <row r="17" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A17" s="33" t="s">
         <v>54</v>
       </c>
@@ -6278,7 +6290,7 @@
       <c r="AW17" s="46"/>
       <c r="AX17" s="31"/>
     </row>
-    <row r="18" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A18" s="33" t="s">
         <v>57</v>
       </c>
@@ -6428,7 +6440,7 @@
       <c r="AV18" s="46"/>
       <c r="AW18" s="46"/>
     </row>
-    <row r="19" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A19" s="211" t="s">
         <v>68</v>
       </c>
@@ -6578,7 +6590,7 @@
       <c r="AV19" s="46"/>
       <c r="AW19" s="46"/>
     </row>
-    <row r="20" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A20" s="211" t="s">
         <v>70</v>
       </c>
@@ -6648,7 +6660,7 @@
       <c r="AV20" s="46"/>
       <c r="AW20" s="46"/>
     </row>
-    <row r="21" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A21" s="33" t="s">
         <v>71</v>
       </c>
@@ -6725,7 +6737,7 @@
       <c r="AV21" s="46"/>
       <c r="AW21" s="46"/>
     </row>
-    <row r="22" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A22" s="33" t="s">
         <v>72</v>
       </c>
@@ -6875,7 +6887,7 @@
       <c r="AV22" s="46"/>
       <c r="AW22" s="46"/>
     </row>
-    <row r="23" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A23" s="33" t="s">
         <v>73</v>
       </c>
@@ -7019,7 +7031,7 @@
       <c r="AV23" s="46"/>
       <c r="AW23" s="46"/>
     </row>
-    <row r="24" spans="1:50" s="45" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:50" s="45" customFormat="1" ht="13">
       <c r="A24" s="33" t="s">
         <v>76</v>
       </c>
@@ -7169,7 +7181,7 @@
       <c r="AV24" s="46"/>
       <c r="AW24" s="46"/>
     </row>
-    <row r="25" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A25" s="33" t="s">
         <v>82</v>
       </c>
@@ -7319,7 +7331,7 @@
       <c r="AV25" s="46"/>
       <c r="AW25" s="46"/>
     </row>
-    <row r="26" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A26" s="33" t="s">
         <v>112</v>
       </c>
@@ -7390,7 +7402,7 @@
       <c r="AV26" s="46"/>
       <c r="AW26" s="46"/>
     </row>
-    <row r="27" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A27" s="33" t="s">
         <v>85</v>
       </c>
@@ -7540,7 +7552,7 @@
       <c r="AV27" s="46"/>
       <c r="AW27" s="46"/>
     </row>
-    <row r="28" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A28" s="33" t="s">
         <v>86</v>
       </c>
@@ -7653,7 +7665,7 @@
       <c r="AV28" s="46"/>
       <c r="AW28" s="46"/>
     </row>
-    <row r="29" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1">
       <c r="A29" s="33" t="s">
         <v>87</v>
       </c>
@@ -7803,7 +7815,7 @@
       <c r="AV29" s="46"/>
       <c r="AW29" s="46"/>
     </row>
-    <row r="30" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:50" s="45" customFormat="1" ht="12" customHeight="1" thickBot="1">
       <c r="A30" s="34" t="s">
         <v>88</v>
       </c>
@@ -7953,7 +7965,7 @@
       <c r="AV30" s="46"/>
       <c r="AW30" s="46"/>
     </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:50">
       <c r="A31" s="213"/>
       <c r="B31" s="214"/>
       <c r="C31" s="214"/>
@@ -8004,17 +8016,12 @@
       <c r="AV31" s="46"/>
       <c r="AW31" s="46"/>
     </row>
-    <row r="36" spans="35:35" x14ac:dyDescent="0.45">
+    <row r="36" spans="35:35">
       <c r="AI36" s="50"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AU30"/>
+  <autoFilter ref="A4:AU30" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="15">
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:P1"/>
     <mergeCell ref="AI1:AK1"/>
     <mergeCell ref="AM1:AO1"/>
     <mergeCell ref="AP1:AR1"/>
@@ -8025,6 +8032,11 @@
     <mergeCell ref="Z1:AB1"/>
     <mergeCell ref="AC1:AE1"/>
     <mergeCell ref="AF1:AH1"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:P1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="65" orientation="landscape" r:id="rId1"/>
@@ -8037,25 +8049,25 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.53125" style="37" customWidth="1"/>
+    <col min="1" max="1" width="27.5" style="37" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" style="37" customWidth="1"/>
-    <col min="3" max="3" width="16.46484375" style="37" customWidth="1"/>
-    <col min="4" max="4" width="16.53125" style="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5" style="37" customWidth="1"/>
+    <col min="4" max="4" width="16.5" style="37" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.6640625" style="37" customWidth="1"/>
-    <col min="6" max="16384" width="9.1328125" style="37"/>
+    <col min="6" max="16384" width="9.1640625" style="37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="16">
       <c r="A1" s="57"/>
       <c r="C1" s="57"/>
       <c r="D1" s="57"/>
       <c r="E1" s="57"/>
     </row>
-    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="16">
       <c r="A2" s="409" t="s">
         <v>511</v>
       </c>
@@ -8064,7 +8076,7 @@
       <c r="D2" s="409"/>
       <c r="E2" s="409"/>
     </row>
-    <row r="3" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" ht="16">
       <c r="A3" s="410" t="s">
         <v>116</v>
       </c>
@@ -8073,7 +8085,7 @@
       <c r="D3" s="410"/>
       <c r="E3" s="410"/>
     </row>
-    <row r="4" spans="1:5" ht="60" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" ht="68">
       <c r="A4" s="58" t="s">
         <v>7</v>
       </c>
@@ -8090,7 +8102,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A5" s="360" t="s">
         <v>22</v>
       </c>
@@ -8107,7 +8119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A6" s="360" t="s">
         <v>23</v>
       </c>
@@ -8124,7 +8136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A7" s="360" t="s">
         <v>103</v>
       </c>
@@ -8135,7 +8147,7 @@
       </c>
       <c r="E7" s="276"/>
     </row>
-    <row r="8" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A8" s="360" t="s">
         <v>29</v>
       </c>
@@ -8152,7 +8164,7 @@
         <v>0.19903155</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A9" s="360" t="s">
         <v>31</v>
       </c>
@@ -8169,7 +8181,7 @@
         <v>888.01</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A10" s="360" t="s">
         <v>33</v>
       </c>
@@ -8186,7 +8198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A11" s="360" t="s">
         <v>45</v>
       </c>
@@ -8199,7 +8211,7 @@
       <c r="D11" s="276"/>
       <c r="E11" s="276"/>
     </row>
-    <row r="12" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A12" s="360" t="s">
         <v>49</v>
       </c>
@@ -8216,7 +8228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A13" s="360" t="s">
         <v>54</v>
       </c>
@@ -8233,7 +8245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A14" s="360" t="s">
         <v>57</v>
       </c>
@@ -8250,7 +8262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A15" s="360" t="s">
         <v>68</v>
       </c>
@@ -8267,7 +8279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A16" s="360" t="s">
         <v>70</v>
       </c>
@@ -8284,7 +8296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A17" s="360" t="s">
         <v>76</v>
       </c>
@@ -8295,7 +8307,7 @@
       <c r="D17" s="276"/>
       <c r="E17" s="276"/>
     </row>
-    <row r="18" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A18" s="360" t="s">
         <v>82</v>
       </c>
@@ -8312,7 +8324,7 @@
         <v>610.83000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A19" s="360" t="s">
         <v>112</v>
       </c>
@@ -8325,7 +8337,7 @@
       <c r="D19" s="276"/>
       <c r="E19" s="276"/>
     </row>
-    <row r="20" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A20" s="360" t="s">
         <v>85</v>
       </c>
@@ -8342,7 +8354,7 @@
         <v>0.48300000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A21" s="360" t="s">
         <v>86</v>
       </c>
@@ -8359,7 +8371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A22" s="360" t="s">
         <v>87</v>
       </c>
@@ -8376,7 +8388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="359" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" s="359" customFormat="1" ht="17">
       <c r="A23" s="360" t="s">
         <v>88</v>
       </c>
@@ -8393,7 +8405,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" ht="17">
       <c r="A24" s="38" t="s">
         <v>232</v>
       </c>
@@ -8414,18 +8426,18 @@
         <v>1500.4920315499999</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5">
       <c r="A28" s="39"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5">
       <c r="B29" s="408"/>
       <c r="C29" s="408"/>
       <c r="D29" s="408"/>
       <c r="E29" s="408"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E24">
-    <sortState ref="A5:G94">
+  <autoFilter ref="A4:E24" xr:uid="{00000000-0009-0000-0000-000009000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:G94">
       <sortCondition ref="A4:A94"/>
     </sortState>
   </autoFilter>
@@ -8445,41 +8457,40 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AA166"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.06640625" style="37"/>
-    <col min="2" max="2" width="36.46484375" style="37" customWidth="1"/>
-    <col min="3" max="3" width="13.46484375" style="37" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="37"/>
+    <col min="2" max="2" width="36.5" style="37" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="37" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" style="37" customWidth="1"/>
-    <col min="5" max="5" width="9.06640625" style="37"/>
-    <col min="6" max="6" width="13.46484375" style="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1328125" style="37" customWidth="1"/>
-    <col min="8" max="8" width="9.06640625" style="37"/>
-    <col min="9" max="9" width="13.53125" style="37" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.86328125" style="37" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.06640625" style="37"/>
+    <col min="5" max="5" width="9" style="37"/>
+    <col min="6" max="6" width="13.5" style="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" style="37" customWidth="1"/>
+    <col min="8" max="8" width="9" style="37"/>
+    <col min="9" max="9" width="13.5" style="37" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" style="37" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" style="37"/>
     <col min="12" max="12" width="16" style="37" customWidth="1"/>
-    <col min="13" max="13" width="14.1328125" style="37" customWidth="1"/>
+    <col min="13" max="13" width="14.1640625" style="37" customWidth="1"/>
     <col min="14" max="14" width="9.6640625" style="37" customWidth="1"/>
-    <col min="15" max="15" width="12.9296875" style="37" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.46484375" style="37" customWidth="1"/>
-    <col min="17" max="17" width="15.53125" style="37" customWidth="1"/>
+    <col min="15" max="15" width="13" style="37" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5" style="37" customWidth="1"/>
+    <col min="17" max="17" width="15.5" style="37" customWidth="1"/>
     <col min="18" max="18" width="10.6640625" style="37" customWidth="1"/>
-    <col min="19" max="19" width="14.19921875" style="37" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.1328125" style="37" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.1640625" style="37" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="9.6640625" style="37" customWidth="1"/>
-    <col min="22" max="22" width="12.9296875" style="37" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.1328125" style="37" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.73046875" style="37" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.9296875" style="37" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.265625" style="37" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.796875" style="37" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.06640625" style="37"/>
+    <col min="22" max="22" width="13" style="37" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.1640625" style="37" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.6640625" style="37" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13" style="37" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.33203125" style="37" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.83203125" style="37" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9" style="37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="31.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:27" ht="31.25" customHeight="1" thickBot="1">
       <c r="A1" s="364"/>
       <c r="B1" s="365"/>
       <c r="C1" s="361" t="s">
@@ -8522,7 +8533,7 @@
       <c r="Z1" s="185"/>
       <c r="AA1" s="185"/>
     </row>
-    <row r="2" spans="1:27" ht="43.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:27" ht="43.25" customHeight="1" thickBot="1">
       <c r="A2" s="364"/>
       <c r="B2" s="365"/>
       <c r="C2" s="165" t="s">
@@ -8593,7 +8604,7 @@
       <c r="Z2" s="185"/>
       <c r="AA2" s="185"/>
     </row>
-    <row r="3" spans="1:27" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:27" ht="16" thickTop="1">
       <c r="A3" s="173"/>
       <c r="B3" s="172" t="s">
         <v>261</v>
@@ -8666,7 +8677,7 @@
       <c r="Z3" s="189"/>
       <c r="AA3" s="189"/>
     </row>
-    <row r="4" spans="1:27" ht="55.9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:27" ht="59">
       <c r="A4" s="79" t="s">
         <v>7</v>
       </c>
@@ -8749,7 +8760,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:27">
       <c r="A5" s="82" t="s">
         <v>260</v>
       </c>
@@ -8782,7 +8793,7 @@
       <c r="Z5" s="83"/>
       <c r="AA5" s="83"/>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:27">
       <c r="A6" s="82" t="s">
         <v>20</v>
       </c>
@@ -8853,7 +8864,7 @@
         <v>42064</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:27">
       <c r="A7" s="82" t="s">
         <v>22</v>
       </c>
@@ -8914,7 +8925,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:27">
       <c r="A8" s="82" t="s">
         <v>22</v>
       </c>
@@ -8979,7 +8990,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:27">
       <c r="A9" s="82" t="s">
         <v>22</v>
       </c>
@@ -9062,7 +9073,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:27">
       <c r="A10" s="82" t="s">
         <v>22</v>
       </c>
@@ -9107,7 +9118,7 @@
       <c r="Z10" s="84"/>
       <c r="AA10" s="84"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:27">
       <c r="A11" s="82" t="s">
         <v>22</v>
       </c>
@@ -9146,7 +9157,7 @@
       <c r="Z11" s="84"/>
       <c r="AA11" s="84"/>
     </row>
-    <row r="12" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:27">
       <c r="A12" s="82" t="s">
         <v>22</v>
       </c>
@@ -9205,7 +9216,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:27">
       <c r="A13" s="82" t="s">
         <v>22</v>
       </c>
@@ -9250,7 +9261,7 @@
       <c r="Z13" s="84"/>
       <c r="AA13" s="84"/>
     </row>
-    <row r="14" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:27">
       <c r="A14" s="82" t="s">
         <v>22</v>
       </c>
@@ -9333,7 +9344,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:27">
       <c r="A15" s="82" t="s">
         <v>22</v>
       </c>
@@ -9398,7 +9409,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:27">
       <c r="A16" s="82" t="s">
         <v>22</v>
       </c>
@@ -9463,7 +9474,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:27">
       <c r="A17" s="82" t="s">
         <v>22</v>
       </c>
@@ -9546,7 +9557,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:27">
       <c r="A18" s="82" t="s">
         <v>22</v>
       </c>
@@ -9611,7 +9622,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:27">
       <c r="A19" s="82" t="s">
         <v>22</v>
       </c>
@@ -9694,7 +9705,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:27">
       <c r="A20" s="82" t="s">
         <v>22</v>
       </c>
@@ -9759,7 +9770,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:27">
       <c r="A21" s="82" t="s">
         <v>22</v>
       </c>
@@ -9842,7 +9853,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:27">
       <c r="A22" s="82" t="s">
         <v>22</v>
       </c>
@@ -9925,7 +9936,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:27">
       <c r="A23" s="82" t="s">
         <v>22</v>
       </c>
@@ -10008,7 +10019,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:27">
       <c r="A24" s="82" t="s">
         <v>22</v>
       </c>
@@ -10059,7 +10070,7 @@
       <c r="Z24" s="84"/>
       <c r="AA24" s="84"/>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:27">
       <c r="A25" s="82" t="s">
         <v>22</v>
       </c>
@@ -10098,7 +10109,7 @@
       <c r="Z25" s="84"/>
       <c r="AA25" s="84"/>
     </row>
-    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:27" ht="24">
       <c r="A26" s="82" t="s">
         <v>22</v>
       </c>
@@ -10137,7 +10148,7 @@
       <c r="Z26" s="84"/>
       <c r="AA26" s="84"/>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:27">
       <c r="A27" s="82" t="s">
         <v>22</v>
       </c>
@@ -10176,7 +10187,7 @@
       <c r="Z27" s="84"/>
       <c r="AA27" s="84"/>
     </row>
-    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:27">
       <c r="A28" s="82" t="s">
         <v>22</v>
       </c>
@@ -10259,7 +10270,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:27">
       <c r="A29" s="82" t="s">
         <v>22</v>
       </c>
@@ -10298,7 +10309,7 @@
       <c r="Z29" s="84"/>
       <c r="AA29" s="84"/>
     </row>
-    <row r="30" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:27">
       <c r="A30" s="82" t="s">
         <v>22</v>
       </c>
@@ -10363,7 +10374,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:27">
       <c r="A31" s="82" t="s">
         <v>22</v>
       </c>
@@ -10428,7 +10439,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:27">
       <c r="A32" s="82" t="s">
         <v>22</v>
       </c>
@@ -10487,7 +10498,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:27">
       <c r="A33" s="82" t="s">
         <v>22</v>
       </c>
@@ -10526,7 +10537,7 @@
       <c r="Z33" s="84"/>
       <c r="AA33" s="84"/>
     </row>
-    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:27">
       <c r="A34" s="82" t="s">
         <v>22</v>
       </c>
@@ -10597,7 +10608,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:27" ht="24">
       <c r="A35" s="82" t="s">
         <v>23</v>
       </c>
@@ -10668,7 +10679,7 @@
         <v>41912</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:27">
       <c r="A36" s="82" t="s">
         <v>24</v>
       </c>
@@ -10751,7 +10762,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:27">
       <c r="A37" s="82" t="s">
         <v>24</v>
       </c>
@@ -10828,7 +10839,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:27">
       <c r="A38" s="82" t="s">
         <v>24</v>
       </c>
@@ -10911,7 +10922,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:27">
       <c r="A39" s="82" t="s">
         <v>24</v>
       </c>
@@ -10994,7 +11005,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:27">
       <c r="A40" s="82" t="s">
         <v>24</v>
       </c>
@@ -11077,7 +11088,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:27">
       <c r="A41" s="82" t="s">
         <v>24</v>
       </c>
@@ -11160,7 +11171,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:27">
       <c r="A42" s="82" t="s">
         <v>24</v>
       </c>
@@ -11237,7 +11248,7 @@
         <v>42156</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:27">
       <c r="A43" s="82" t="s">
         <v>24</v>
       </c>
@@ -11314,7 +11325,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:27">
       <c r="A44" s="82" t="s">
         <v>24</v>
       </c>
@@ -11397,7 +11408,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:27">
       <c r="A45" s="97" t="s">
         <v>27</v>
       </c>
@@ -11462,7 +11473,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:27">
       <c r="A46" s="82" t="s">
         <v>29</v>
       </c>
@@ -11531,7 +11542,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:27">
       <c r="A47" s="82" t="s">
         <v>29</v>
       </c>
@@ -11598,7 +11609,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:27">
       <c r="A48" s="97" t="s">
         <v>31</v>
       </c>
@@ -11669,7 +11680,7 @@
         <v>42156</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:27" ht="24">
       <c r="A49" s="97" t="s">
         <v>31</v>
       </c>
@@ -11708,7 +11719,7 @@
       <c r="Z49" s="84"/>
       <c r="AA49" s="84"/>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:27">
       <c r="A50" s="82" t="s">
         <v>31</v>
       </c>
@@ -11791,7 +11802,7 @@
         <v>42156</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:27">
       <c r="A51" s="82" t="s">
         <v>31</v>
       </c>
@@ -11858,7 +11869,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:27">
       <c r="A52" s="82" t="s">
         <v>33</v>
       </c>
@@ -11941,7 +11952,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:27">
       <c r="A53" s="97" t="s">
         <v>33</v>
       </c>
@@ -12010,7 +12021,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:27">
       <c r="A54" s="97" t="s">
         <v>33</v>
       </c>
@@ -12049,7 +12060,7 @@
       <c r="Z54" s="84"/>
       <c r="AA54" s="84"/>
     </row>
-    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:27">
       <c r="A55" s="82" t="s">
         <v>33</v>
       </c>
@@ -12132,7 +12143,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:27">
       <c r="A56" s="97" t="s">
         <v>33</v>
       </c>
@@ -12197,7 +12208,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:27">
       <c r="A57" s="97" t="s">
         <v>33</v>
       </c>
@@ -12236,7 +12247,7 @@
       <c r="Z57" s="84"/>
       <c r="AA57" s="84"/>
     </row>
-    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:27">
       <c r="A58" s="97" t="s">
         <v>33</v>
       </c>
@@ -12307,7 +12318,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:27">
       <c r="A59" s="82" t="s">
         <v>33</v>
       </c>
@@ -12358,7 +12369,7 @@
       <c r="Z59" s="84"/>
       <c r="AA59" s="84"/>
     </row>
-    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:27">
       <c r="A60" s="97" t="s">
         <v>33</v>
       </c>
@@ -12429,7 +12440,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:27">
       <c r="A61" s="82" t="s">
         <v>33</v>
       </c>
@@ -12512,7 +12523,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:27">
       <c r="A62" s="97" t="s">
         <v>33</v>
       </c>
@@ -12571,7 +12582,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:27">
       <c r="A63" s="82" t="s">
         <v>33</v>
       </c>
@@ -12604,7 +12615,7 @@
       <c r="Z63" s="84"/>
       <c r="AA63" s="84"/>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:27">
       <c r="A64" s="82" t="s">
         <v>42</v>
       </c>
@@ -12681,7 +12692,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:27">
       <c r="A65" s="82" t="s">
         <v>42</v>
       </c>
@@ -12726,7 +12737,7 @@
       <c r="Z65" s="84"/>
       <c r="AA65" s="84"/>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:27">
       <c r="A66" s="82" t="s">
         <v>42</v>
       </c>
@@ -12809,7 +12820,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:27">
       <c r="A67" s="82" t="s">
         <v>42</v>
       </c>
@@ -12892,7 +12903,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:27">
       <c r="A68" s="82" t="s">
         <v>45</v>
       </c>
@@ -12931,7 +12942,7 @@
       <c r="Z68" s="84"/>
       <c r="AA68" s="84"/>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:27">
       <c r="A69" s="82" t="s">
         <v>45</v>
       </c>
@@ -13008,7 +13019,7 @@
         <v>41883</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:27">
       <c r="A70" s="82" t="s">
         <v>45</v>
       </c>
@@ -13085,7 +13096,7 @@
         <v>41883</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:27">
       <c r="A71" s="82" t="s">
         <v>45</v>
       </c>
@@ -13156,7 +13167,7 @@
         <v>41883</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:27">
       <c r="A72" s="82" t="s">
         <v>49</v>
       </c>
@@ -13239,7 +13250,7 @@
         <v>42156</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:27">
       <c r="A73" s="82" t="s">
         <v>49</v>
       </c>
@@ -13322,7 +13333,7 @@
         <v>41974</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:27">
       <c r="A74" s="82" t="s">
         <v>49</v>
       </c>
@@ -13391,7 +13402,7 @@
         <v>41974</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:27">
       <c r="A75" s="82" t="s">
         <v>49</v>
       </c>
@@ -13472,7 +13483,7 @@
         <v>41974</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:27">
       <c r="A76" s="82" t="s">
         <v>54</v>
       </c>
@@ -13549,7 +13560,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:27">
       <c r="A77" s="97" t="s">
         <v>54</v>
       </c>
@@ -13620,7 +13631,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:27">
       <c r="A78" s="82" t="s">
         <v>54</v>
       </c>
@@ -13665,7 +13676,7 @@
       <c r="Z78" s="84"/>
       <c r="AA78" s="84"/>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:27">
       <c r="A79" s="82" t="s">
         <v>54</v>
       </c>
@@ -13710,7 +13721,7 @@
       <c r="Z79" s="84"/>
       <c r="AA79" s="84"/>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:27">
       <c r="A80" s="82" t="s">
         <v>54</v>
       </c>
@@ -13787,7 +13798,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:27">
       <c r="A81" s="82" t="s">
         <v>54</v>
       </c>
@@ -13864,7 +13875,7 @@
         <v>42248</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:27">
       <c r="A82" s="97" t="s">
         <v>57</v>
       </c>
@@ -13917,7 +13928,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:27">
       <c r="A83" s="146" t="s">
         <v>57</v>
       </c>
@@ -13988,7 +13999,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:27">
       <c r="A84" s="97" t="s">
         <v>57</v>
       </c>
@@ -14053,7 +14064,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:27">
       <c r="A85" s="97" t="s">
         <v>57</v>
       </c>
@@ -14112,7 +14123,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:27">
       <c r="A86" s="97" t="s">
         <v>57</v>
       </c>
@@ -14165,7 +14176,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:27">
       <c r="A87" s="82" t="s">
         <v>57</v>
       </c>
@@ -14248,7 +14259,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:27">
       <c r="A88" s="82" t="s">
         <v>57</v>
       </c>
@@ -14331,7 +14342,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:27">
       <c r="A89" s="82" t="s">
         <v>57</v>
       </c>
@@ -14414,7 +14425,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:27">
       <c r="A90" s="82" t="s">
         <v>57</v>
       </c>
@@ -14497,7 +14508,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:27">
       <c r="A91" s="82" t="s">
         <v>57</v>
       </c>
@@ -14580,7 +14591,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:27">
       <c r="A92" s="82" t="s">
         <v>57</v>
       </c>
@@ -14663,7 +14674,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:27">
       <c r="A93" s="82" t="s">
         <v>57</v>
       </c>
@@ -14746,7 +14757,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="30.4" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:27" ht="36">
       <c r="A94" s="97" t="s">
         <v>57</v>
       </c>
@@ -14805,7 +14816,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:27">
       <c r="A95" s="97" t="s">
         <v>57</v>
       </c>
@@ -14864,7 +14875,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:27">
       <c r="A96" s="97" t="s">
         <v>68</v>
       </c>
@@ -14935,7 +14946,7 @@
         <v>41883</v>
       </c>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:27">
       <c r="A97" s="82" t="s">
         <v>68</v>
       </c>
@@ -15018,7 +15029,7 @@
         <v>41883</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:27">
       <c r="A98" s="97" t="s">
         <v>70</v>
       </c>
@@ -15079,7 +15090,7 @@
         <v>41883</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:27">
       <c r="A99" s="82" t="s">
         <v>71</v>
       </c>
@@ -15118,7 +15129,7 @@
       <c r="Z99" s="84"/>
       <c r="AA99" s="84"/>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:27">
       <c r="A100" s="82" t="s">
         <v>72</v>
       </c>
@@ -15157,7 +15168,7 @@
       <c r="Z100" s="84"/>
       <c r="AA100" s="84"/>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:27">
       <c r="A101" s="82" t="s">
         <v>72</v>
       </c>
@@ -15196,7 +15207,7 @@
       <c r="Z101" s="84"/>
       <c r="AA101" s="84"/>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:27">
       <c r="A102" s="82" t="s">
         <v>72</v>
       </c>
@@ -15279,7 +15290,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:27">
       <c r="A103" s="82" t="s">
         <v>72</v>
       </c>
@@ -15362,7 +15373,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:27">
       <c r="A104" s="82" t="s">
         <v>73</v>
       </c>
@@ -15445,7 +15456,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:27">
       <c r="A105" s="82" t="s">
         <v>73</v>
       </c>
@@ -15516,7 +15527,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:27">
       <c r="A106" s="82" t="s">
         <v>76</v>
       </c>
@@ -15599,7 +15610,7 @@
         <v>42064</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:27">
       <c r="A107" s="82" t="s">
         <v>76</v>
       </c>
@@ -15682,7 +15693,7 @@
         <v>42064</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:27">
       <c r="A108" s="82" t="s">
         <v>76</v>
       </c>
@@ -15765,7 +15776,7 @@
         <v>42064</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:27">
       <c r="A109" s="82" t="s">
         <v>76</v>
       </c>
@@ -15848,7 +15859,7 @@
         <v>42156</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:27">
       <c r="A110" s="82" t="s">
         <v>76</v>
       </c>
@@ -15931,7 +15942,7 @@
         <v>42064</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:27" ht="24">
       <c r="A111" s="82" t="s">
         <v>76</v>
       </c>
@@ -15992,7 +16003,7 @@
         <v>41671</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:27" ht="24">
       <c r="A112" s="82" t="s">
         <v>76</v>
       </c>
@@ -16053,7 +16064,7 @@
         <v>41671</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:27" ht="24">
       <c r="A113" s="82" t="s">
         <v>76</v>
       </c>
@@ -16114,7 +16125,7 @@
         <v>41671</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:27">
       <c r="A114" s="97" t="s">
         <v>76</v>
       </c>
@@ -16181,7 +16192,7 @@
         <v>42064</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:27">
       <c r="A115" s="82" t="s">
         <v>82</v>
       </c>
@@ -16244,7 +16255,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:27">
       <c r="A116" s="82" t="s">
         <v>82</v>
       </c>
@@ -16327,7 +16338,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:27">
       <c r="A117" s="82" t="s">
         <v>82</v>
       </c>
@@ -16410,7 +16421,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:27">
       <c r="A118" s="82" t="s">
         <v>85</v>
       </c>
@@ -16493,7 +16504,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:27">
       <c r="A119" s="82" t="s">
         <v>86</v>
       </c>
@@ -16544,7 +16555,7 @@
       <c r="Z119" s="84"/>
       <c r="AA119" s="84"/>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:27">
       <c r="A120" s="82" t="s">
         <v>87</v>
       </c>
@@ -16589,7 +16600,7 @@
       <c r="Z120" s="84"/>
       <c r="AA120" s="84"/>
     </row>
-    <row r="121" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:27">
       <c r="A121" s="82" t="s">
         <v>87</v>
       </c>
@@ -16673,7 +16684,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:27">
       <c r="A122" s="97" t="s">
         <v>87</v>
       </c>
@@ -16712,7 +16723,7 @@
       <c r="Z122" s="84"/>
       <c r="AA122" s="84"/>
     </row>
-    <row r="123" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:27">
       <c r="A123" s="82" t="s">
         <v>87</v>
       </c>
@@ -16795,7 +16806,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:27">
       <c r="A124" s="82" t="s">
         <v>87</v>
       </c>
@@ -16878,7 +16889,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:27" ht="24">
       <c r="A125" s="82" t="s">
         <v>87</v>
       </c>
@@ -16961,7 +16972,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:27">
       <c r="A126" s="82" t="s">
         <v>87</v>
       </c>
@@ -17044,7 +17055,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:27" ht="24">
       <c r="A127" s="97" t="s">
         <v>87</v>
       </c>
@@ -17103,7 +17114,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="128" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:27">
       <c r="A128" s="97" t="s">
         <v>87</v>
       </c>
@@ -17156,7 +17167,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:27">
       <c r="A129" s="82" t="s">
         <v>87</v>
       </c>
@@ -17207,7 +17218,7 @@
       <c r="Z129" s="84"/>
       <c r="AA129" s="84"/>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:27">
       <c r="A130" s="82" t="s">
         <v>87</v>
       </c>
@@ -17252,7 +17263,7 @@
       <c r="Z130" s="84"/>
       <c r="AA130" s="84"/>
     </row>
-    <row r="131" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:27" ht="24">
       <c r="A131" s="97" t="s">
         <v>87</v>
       </c>
@@ -17319,7 +17330,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="132" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:27" ht="24">
       <c r="A132" s="82" t="s">
         <v>87</v>
       </c>
@@ -17384,7 +17395,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="133" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:27">
       <c r="A133" s="82" t="s">
         <v>87</v>
       </c>
@@ -17449,7 +17460,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="134" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:27">
       <c r="A134" s="82" t="s">
         <v>87</v>
       </c>
@@ -17514,7 +17525,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:27">
       <c r="A135" s="97" t="s">
         <v>87</v>
       </c>
@@ -17571,7 +17582,7 @@
       <c r="Z135" s="298"/>
       <c r="AA135" s="298"/>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:27">
       <c r="A136" s="82" t="s">
         <v>87</v>
       </c>
@@ -17616,7 +17627,7 @@
       <c r="Z136" s="84"/>
       <c r="AA136" s="84"/>
     </row>
-    <row r="137" spans="1:27" ht="50.65" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:27" ht="60">
       <c r="A137" s="82" t="s">
         <v>87</v>
       </c>
@@ -17699,7 +17710,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="138" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:27" ht="24">
       <c r="A138" s="97" t="s">
         <v>87</v>
       </c>
@@ -17764,7 +17775,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:27">
       <c r="A139" s="82" t="s">
         <v>87</v>
       </c>
@@ -17809,7 +17820,7 @@
       <c r="Z139" s="84"/>
       <c r="AA139" s="84"/>
     </row>
-    <row r="140" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:27" ht="24">
       <c r="A140" s="82" t="s">
         <v>87</v>
       </c>
@@ -17892,7 +17903,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="141" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:27" ht="24">
       <c r="A141" s="97" t="s">
         <v>87</v>
       </c>
@@ -17957,7 +17968,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="142" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:27">
       <c r="A142" s="82" t="s">
         <v>87</v>
       </c>
@@ -18040,7 +18051,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="143" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:27" ht="24">
       <c r="A143" s="82" t="s">
         <v>87</v>
       </c>
@@ -18123,7 +18134,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="144" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:27">
       <c r="A144" s="82" t="s">
         <v>88</v>
       </c>
@@ -18200,7 +18211,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="145" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:27">
       <c r="A145" s="82" t="s">
         <v>88</v>
       </c>
@@ -18283,7 +18294,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="146" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:27">
       <c r="A146" s="82" t="s">
         <v>88</v>
       </c>
@@ -18360,7 +18371,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:27">
       <c r="A147" s="82" t="s">
         <v>88</v>
       </c>
@@ -18399,7 +18410,7 @@
       <c r="Z147" s="84"/>
       <c r="AA147" s="84"/>
     </row>
-    <row r="148" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:27">
       <c r="A148" s="82" t="s">
         <v>88</v>
       </c>
@@ -18470,7 +18481,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:27">
       <c r="A149" s="82" t="s">
         <v>88</v>
       </c>
@@ -18509,7 +18520,7 @@
       <c r="Z149" s="84"/>
       <c r="AA149" s="84"/>
     </row>
-    <row r="150" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:27">
       <c r="A150" s="82" t="s">
         <v>88</v>
       </c>
@@ -18586,7 +18597,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="151" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:27">
       <c r="A151" s="82" t="s">
         <v>88</v>
       </c>
@@ -18663,7 +18674,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="152" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:27">
       <c r="A152" s="82" t="s">
         <v>88</v>
       </c>
@@ -18740,7 +18751,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:27">
       <c r="A153" s="82" t="s">
         <v>88</v>
       </c>
@@ -18785,7 +18796,7 @@
       <c r="Z153" s="84"/>
       <c r="AA153" s="84"/>
     </row>
-    <row r="154" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:27">
       <c r="A154" s="82" t="s">
         <v>88</v>
       </c>
@@ -18862,7 +18873,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="155" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:27">
       <c r="A155" s="97" t="s">
         <v>88</v>
       </c>
@@ -18933,7 +18944,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="156" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:27">
       <c r="A156" s="97" t="s">
         <v>88</v>
       </c>
@@ -19004,7 +19015,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="157" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:27">
       <c r="A157" s="82" t="s">
         <v>88</v>
       </c>
@@ -19087,7 +19098,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="158" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:27">
       <c r="A158" s="82" t="s">
         <v>88</v>
       </c>
@@ -19170,7 +19181,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="159" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:27">
       <c r="A159" s="97" t="s">
         <v>88</v>
       </c>
@@ -19241,7 +19252,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="160" spans="1:27" ht="20.25" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:27">
       <c r="A160" s="82" t="s">
         <v>88</v>
       </c>
@@ -19324,7 +19335,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="161" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:27">
       <c r="A161" s="185"/>
       <c r="B161" s="185"/>
       <c r="C161" s="186"/>
@@ -19353,7 +19364,7 @@
       <c r="Z161" s="185"/>
       <c r="AA161" s="185"/>
     </row>
-    <row r="162" spans="1:27" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:27" ht="16" thickBot="1">
       <c r="A162" s="101"/>
       <c r="B162" s="181" t="s">
         <v>251</v>
@@ -19412,17 +19423,17 @@
       <c r="Z162" s="78"/>
       <c r="AA162" s="78"/>
     </row>
-    <row r="163" spans="1:27" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
-    <row r="165" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:27" ht="16" thickTop="1"/>
+    <row r="165" spans="1:27">
       <c r="L165" s="184"/>
       <c r="M165" s="184"/>
     </row>
-    <row r="166" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:27">
       <c r="D166" s="184"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AA160">
-    <sortState ref="A5:AA160">
+  <autoFilter ref="A4:AA160" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:AA160">
       <sortCondition ref="A4:A160"/>
     </sortState>
   </autoFilter>
@@ -19447,9 +19458,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AW23"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="11.65" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="44" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" style="44" customWidth="1"/>
@@ -19457,24 +19468,24 @@
     <col min="30" max="32" width="13" style="44" customWidth="1"/>
     <col min="33" max="33" width="13" style="44" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="13" style="44" customWidth="1"/>
-    <col min="35" max="35" width="10.53125" style="44" customWidth="1"/>
-    <col min="36" max="36" width="13.1328125" style="44" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.5" style="44" customWidth="1"/>
+    <col min="36" max="36" width="13.1640625" style="44" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="13" style="44" customWidth="1"/>
     <col min="38" max="39" width="8.6640625" style="44"/>
-    <col min="40" max="40" width="11.73046875" style="326" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="11.1328125" style="326" customWidth="1"/>
-    <col min="42" max="42" width="10.53125" style="322" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="11.73046875" style="326" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.1328125" style="326" customWidth="1"/>
-    <col min="45" max="45" width="10.53125" style="322" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11.73046875" style="326" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="11.1328125" style="326" customWidth="1"/>
-    <col min="48" max="48" width="10.53125" style="322" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.6640625" style="326" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="11.1640625" style="326" customWidth="1"/>
+    <col min="42" max="42" width="10.5" style="322" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="11.6640625" style="326" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.1640625" style="326" customWidth="1"/>
+    <col min="45" max="45" width="10.5" style="322" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11.6640625" style="326" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="11.1640625" style="326" customWidth="1"/>
+    <col min="48" max="48" width="10.5" style="322" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="8.6640625" style="48"/>
     <col min="50" max="16384" width="8.6640625" style="44"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" s="61" customFormat="1" ht="34.9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:48" s="61" customFormat="1" ht="39">
       <c r="A1" s="67" t="s">
         <v>7</v>
       </c>
@@ -19618,7 +19629,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:48" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:48" s="61" customFormat="1" ht="13">
       <c r="A2" s="62" t="s">
         <v>57</v>
       </c>
@@ -19762,7 +19773,7 @@
         <v>9.3999993399514203E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:48" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:48" s="61" customFormat="1" ht="13">
       <c r="A3" s="62" t="s">
         <v>57</v>
       </c>
@@ -19882,7 +19893,7 @@
         <v>7.3600009789997423E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:48" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:48" s="61" customFormat="1" ht="13">
       <c r="A4" s="62" t="s">
         <v>85</v>
       </c>
@@ -20026,7 +20037,7 @@
         <v>0.23749999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:48" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:48" s="61" customFormat="1" ht="13">
       <c r="A5" s="62" t="s">
         <v>57</v>
       </c>
@@ -20146,7 +20157,7 @@
         <v>8.7904974996031129E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:48" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:48" s="61" customFormat="1" ht="13">
       <c r="A6" s="62" t="s">
         <v>82</v>
       </c>
@@ -20290,7 +20301,7 @@
         <v>4.0000037238203789E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:48" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:48" s="61" customFormat="1" ht="13">
       <c r="A7" s="62" t="s">
         <v>82</v>
       </c>
@@ -20434,7 +20445,7 @@
         <v>6.1999947595344773E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:48" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:48" s="61" customFormat="1" ht="13">
       <c r="A8" s="62" t="s">
         <v>31</v>
       </c>
@@ -20578,7 +20589,7 @@
         <v>0.10429878295598673</v>
       </c>
     </row>
-    <row r="9" spans="1:48" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:48" s="61" customFormat="1" ht="13">
       <c r="A9" s="62" t="s">
         <v>87</v>
       </c>
@@ -20722,7 +20733,7 @@
         <v>3.659766718286047E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:48" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:48" s="61" customFormat="1" ht="13">
       <c r="A10" s="283" t="s">
         <v>57</v>
       </c>
@@ -20824,7 +20835,7 @@
         <v>3.2000020536200185E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:48" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:48" s="61" customFormat="1">
       <c r="A11" s="284" t="s">
         <v>88</v>
       </c>
@@ -20908,7 +20919,7 @@
         <v>0.47000081872302601</v>
       </c>
     </row>
-    <row r="12" spans="1:48" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:48" s="61" customFormat="1" ht="13">
       <c r="A12" s="62" t="s">
         <v>87</v>
       </c>
@@ -21034,7 +21045,7 @@
         <v>0.14076201261931726</v>
       </c>
     </row>
-    <row r="13" spans="1:48" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:48" s="61" customFormat="1" ht="13">
       <c r="A13" s="62" t="s">
         <v>88</v>
       </c>
@@ -21124,7 +21135,7 @@
         <v>2.3299997079219644E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:48" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:48" s="61" customFormat="1" ht="13">
       <c r="A14" s="62" t="s">
         <v>42</v>
       </c>
@@ -21214,7 +21225,7 @@
         <v>1.2799944426595346E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:48" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:48" s="61" customFormat="1" ht="13">
       <c r="A15" s="283" t="s">
         <v>68</v>
       </c>
@@ -21358,7 +21369,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:48" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:48" s="61" customFormat="1">
       <c r="A16" s="284" t="s">
         <v>88</v>
       </c>
@@ -21442,7 +21453,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="17" spans="1:49" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:49" s="61" customFormat="1" ht="13">
       <c r="A17" s="62" t="s">
         <v>87</v>
       </c>
@@ -21568,7 +21579,7 @@
         <v>0.20754137115839244</v>
       </c>
     </row>
-    <row r="18" spans="1:49" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:49" s="61" customFormat="1" ht="13">
       <c r="A18" s="62" t="s">
         <v>76</v>
       </c>
@@ -21688,7 +21699,7 @@
         <v>4.5500317460317463E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:49" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:49" s="61" customFormat="1" ht="13">
       <c r="A19" s="62" t="s">
         <v>57</v>
       </c>
@@ -21790,7 +21801,7 @@
         <v>5.8999764677418472E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:49" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:49" s="61" customFormat="1" ht="13">
       <c r="A20" s="62" t="s">
         <v>42</v>
       </c>
@@ -21934,7 +21945,7 @@
         <v>1.8499876938222991E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:49" s="61" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:49" s="61" customFormat="1" ht="13">
       <c r="A21" s="62" t="s">
         <v>87</v>
       </c>
@@ -22078,7 +22089,7 @@
         <v>2.1701687909059592E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:49" s="60" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:49" s="60" customFormat="1">
       <c r="C22" s="118"/>
       <c r="D22" s="66"/>
       <c r="E22" s="119"/>
@@ -22125,7 +22136,7 @@
       <c r="AV22" s="322"/>
       <c r="AW22" s="132"/>
     </row>
-    <row r="23" spans="1:49" s="60" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:49" s="60" customFormat="1" ht="13" thickBot="1">
       <c r="A23" s="220"/>
       <c r="B23" s="233" t="s">
         <v>379</v>
@@ -22268,8 +22279,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AW21">
-    <sortState ref="A2:AV21">
+  <autoFilter ref="A1:AW21" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AV21">
       <sortCondition descending="1" ref="AK1:AK21"/>
     </sortState>
   </autoFilter>
@@ -22284,22 +22295,22 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H36"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.86328125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="16.53125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="15.53125" style="21" customWidth="1"/>
-    <col min="4" max="4" width="16.53125" style="21" customWidth="1"/>
-    <col min="5" max="5" width="14.86328125" style="21" customWidth="1"/>
-    <col min="6" max="6" width="16.46484375" style="21" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="16.5" style="5" customWidth="1"/>
+    <col min="3" max="3" width="15.5" style="21" customWidth="1"/>
+    <col min="4" max="4" width="16.5" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" style="21" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="21" customWidth="1"/>
     <col min="7" max="7" width="9" style="5" customWidth="1"/>
     <col min="8" max="8" width="6.33203125" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="9.1328125" style="5"/>
+    <col min="9" max="16384" width="9.1640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="369" t="s">
         <v>153</v>
       </c>
@@ -22309,7 +22320,7 @@
       <c r="E1" s="369"/>
       <c r="F1" s="369"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="370"/>
       <c r="B2" s="370"/>
       <c r="C2" s="370"/>
@@ -22317,7 +22328,7 @@
       <c r="E2" s="370"/>
       <c r="F2" s="370"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" ht="16">
       <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
@@ -22337,7 +22348,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" ht="16">
       <c r="A4" s="8" t="s">
         <v>22</v>
       </c>
@@ -22357,7 +22368,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" ht="15" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>23</v>
       </c>
@@ -22378,7 +22389,7 @@
       </c>
       <c r="H5" s="11"/>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1">
       <c r="A6" s="12" t="s">
         <v>24</v>
       </c>
@@ -22398,7 +22409,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" ht="17.25" customHeight="1">
       <c r="A7" s="12" t="s">
         <v>103</v>
       </c>
@@ -22418,7 +22429,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" ht="16">
       <c r="A8" s="12" t="s">
         <v>27</v>
       </c>
@@ -22439,7 +22450,7 @@
       </c>
       <c r="G8" s="13"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" ht="16">
       <c r="A9" s="12" t="s">
         <v>29</v>
       </c>
@@ -22459,7 +22470,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" ht="16">
       <c r="A10" s="12" t="s">
         <v>31</v>
       </c>
@@ -22479,7 +22490,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" ht="16">
       <c r="A11" s="12" t="s">
         <v>33</v>
       </c>
@@ -22499,7 +22510,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" ht="16">
       <c r="A12" s="14" t="s">
         <v>42</v>
       </c>
@@ -22519,7 +22530,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" ht="16">
       <c r="A13" s="14" t="s">
         <v>45</v>
       </c>
@@ -22539,7 +22550,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" ht="16">
       <c r="A14" s="14" t="s">
         <v>54</v>
       </c>
@@ -22559,7 +22570,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" ht="16.5" customHeight="1">
       <c r="A15" s="14" t="s">
         <v>57</v>
       </c>
@@ -22579,7 +22590,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" ht="16">
       <c r="A16" s="14" t="s">
         <v>68</v>
       </c>
@@ -22599,7 +22610,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" ht="16">
       <c r="A17" s="14" t="s">
         <v>70</v>
       </c>
@@ -22619,7 +22630,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" ht="16">
       <c r="A18" s="14" t="s">
         <v>102</v>
       </c>
@@ -22639,7 +22650,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" ht="13.5" customHeight="1">
       <c r="A19" s="14" t="s">
         <v>71</v>
       </c>
@@ -22660,7 +22671,7 @@
       </c>
       <c r="G19" s="16"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" ht="16">
       <c r="A20" s="14" t="s">
         <v>72</v>
       </c>
@@ -22680,7 +22691,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" ht="16">
       <c r="A21" s="14" t="s">
         <v>76</v>
       </c>
@@ -22700,7 +22711,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" ht="16">
       <c r="A22" s="10" t="s">
         <v>82</v>
       </c>
@@ -22720,7 +22731,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" s="20" customFormat="1">
       <c r="A23" s="17" t="s">
         <v>112</v>
       </c>
@@ -22741,7 +22752,7 @@
       </c>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:8" ht="16">
       <c r="A24" s="14" t="s">
         <v>85</v>
       </c>
@@ -22761,7 +22772,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" ht="16">
       <c r="A25" s="14" t="s">
         <v>86</v>
       </c>
@@ -22781,7 +22792,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:8" ht="16">
       <c r="A26" s="14" t="s">
         <v>87</v>
       </c>
@@ -22801,7 +22812,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" ht="16">
       <c r="A27" s="14" t="s">
         <v>88</v>
       </c>
@@ -22821,7 +22832,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" ht="8.25" customHeight="1">
       <c r="C28" s="21" t="s">
         <v>113</v>
       </c>
@@ -22835,7 +22846,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" ht="16">
       <c r="B29" s="7" t="s">
         <v>104</v>
       </c>
@@ -22852,7 +22863,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" ht="16">
       <c r="A30" s="14" t="s">
         <v>110</v>
       </c>
@@ -22872,7 +22883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" ht="16">
       <c r="A31" s="14" t="s">
         <v>114</v>
       </c>
@@ -22892,7 +22903,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:8" ht="16">
       <c r="A32" s="10" t="s">
         <v>110</v>
       </c>
@@ -22912,7 +22923,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" ht="16">
       <c r="A33" s="10" t="s">
         <v>114</v>
       </c>
@@ -22932,7 +22943,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" ht="16">
       <c r="A34" s="10" t="s">
         <v>115</v>
       </c>
@@ -22952,16 +22963,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6">
       <c r="A36" s="234"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F27"/>
+  <autoFilter ref="A3:F27" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:F27">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:F27" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>$H$4:$H$7</formula1>
     </dataValidation>
   </dataValidations>
@@ -22977,30 +22988,29 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q232"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.53125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="13.86328125" style="23" customWidth="1"/>
-    <col min="4" max="4" width="14.46484375" style="23" customWidth="1"/>
+    <col min="1" max="1" width="8.5" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5" style="23" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="14.5" style="23" customWidth="1"/>
     <col min="5" max="5" width="13" style="23" customWidth="1"/>
-    <col min="6" max="6" width="10.53125" style="23" customWidth="1"/>
-    <col min="7" max="7" width="11.53125" style="23" customWidth="1"/>
-    <col min="8" max="8" width="11.46484375" style="23" customWidth="1"/>
-    <col min="9" max="9" width="10.53125" style="23" customWidth="1"/>
-    <col min="10" max="11" width="12.53125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="10.5" style="23" customWidth="1"/>
+    <col min="7" max="8" width="11.5" style="23" customWidth="1"/>
+    <col min="9" max="9" width="10.5" style="23" customWidth="1"/>
+    <col min="10" max="11" width="12.5" style="23" customWidth="1"/>
     <col min="12" max="12" width="14" style="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.86328125" style="23" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.53125" style="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5" style="23" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" style="23" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.53125" style="23" customWidth="1"/>
-    <col min="17" max="17" width="17.53125" style="23" customWidth="1"/>
-    <col min="18" max="16384" width="9.1328125" style="102"/>
+    <col min="16" max="16" width="11.5" style="23" customWidth="1"/>
+    <col min="17" max="17" width="17.5" style="23" customWidth="1"/>
+    <col min="18" max="16384" width="9.1640625" style="102"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="21" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:17" ht="21">
       <c r="A1" s="371" t="s">
         <v>466</v>
       </c>
@@ -23021,7 +23031,7 @@
       <c r="P1" s="371"/>
       <c r="Q1" s="371"/>
     </row>
-    <row r="3" spans="1:17" s="26" customFormat="1" ht="126.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" s="26" customFormat="1" ht="126.75" customHeight="1">
       <c r="A3" s="35" t="s">
         <v>7</v>
       </c>
@@ -23074,7 +23084,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17" ht="17">
       <c r="A4" s="285" t="s">
         <v>20</v>
       </c>
@@ -23107,7 +23117,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17" ht="14.5" customHeight="1">
       <c r="A5" s="285" t="s">
         <v>20</v>
       </c>
@@ -23136,7 +23146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:17" ht="34">
       <c r="A6" s="285" t="s">
         <v>22</v>
       </c>
@@ -23189,7 +23199,7 @@
         <v>3.8759999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" ht="34">
       <c r="A7" s="285" t="s">
         <v>22</v>
       </c>
@@ -23240,7 +23250,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:17" ht="15.5" customHeight="1">
       <c r="A8" s="285" t="s">
         <v>22</v>
       </c>
@@ -23293,7 +23303,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:17" ht="17">
       <c r="A9" s="285" t="s">
         <v>22</v>
       </c>
@@ -23344,7 +23354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:17" ht="17">
       <c r="A10" s="285" t="s">
         <v>22</v>
       </c>
@@ -23397,7 +23407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:17" ht="17">
       <c r="A11" s="285" t="s">
         <v>22</v>
       </c>
@@ -23448,7 +23458,7 @@
         <v>6.9999999999999999E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:17" ht="34">
       <c r="A12" s="285" t="s">
         <v>22</v>
       </c>
@@ -23501,7 +23511,7 @@
         <v>1.444</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:17" ht="34">
       <c r="A13" s="285" t="s">
         <v>22</v>
       </c>
@@ -23550,7 +23560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:17" ht="34">
       <c r="A14" s="285" t="s">
         <v>22</v>
       </c>
@@ -23603,7 +23613,7 @@
         <v>10.92</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:17" ht="34">
       <c r="A15" s="285" t="s">
         <v>22</v>
       </c>
@@ -23654,7 +23664,7 @@
         <v>8.0000000000000007E-5</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:17" ht="51">
       <c r="A16" s="285" t="s">
         <v>22</v>
       </c>
@@ -23707,7 +23717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:17" ht="51">
       <c r="A17" s="285" t="s">
         <v>22</v>
       </c>
@@ -23758,7 +23768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:17" ht="51">
       <c r="A18" s="285" t="s">
         <v>22</v>
       </c>
@@ -23811,7 +23821,7 @@
         <v>17.96</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:17" ht="51">
       <c r="A19" s="285" t="s">
         <v>22</v>
       </c>
@@ -23862,7 +23872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:17" ht="34">
       <c r="A20" s="285" t="s">
         <v>22</v>
       </c>
@@ -23915,7 +23925,7 @@
         <v>1.5580000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:17" ht="34">
       <c r="A21" s="285" t="s">
         <v>22</v>
       </c>
@@ -23966,7 +23976,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:17" ht="34">
       <c r="A22" s="285" t="s">
         <v>22</v>
       </c>
@@ -24019,7 +24029,7 @@
         <v>1.3540000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:17" ht="34">
       <c r="A23" s="285" t="s">
         <v>22</v>
       </c>
@@ -24070,7 +24080,7 @@
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="31.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:17" ht="31.25" customHeight="1">
       <c r="A24" s="285" t="s">
         <v>22</v>
       </c>
@@ -24123,7 +24133,7 @@
         <v>2.0220000000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="31.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:17" ht="31.25" customHeight="1">
       <c r="A25" s="285" t="s">
         <v>22</v>
       </c>
@@ -24174,7 +24184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:17" ht="34">
       <c r="A26" s="285" t="s">
         <v>22</v>
       </c>
@@ -24227,7 +24237,7 @@
         <v>56.58</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:17" ht="34">
       <c r="A27" s="285" t="s">
         <v>22</v>
       </c>
@@ -24278,7 +24288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:17" ht="51">
       <c r="A28" s="285" t="s">
         <v>22</v>
       </c>
@@ -24331,7 +24341,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:17" ht="51">
       <c r="A29" s="285" t="s">
         <v>22</v>
       </c>
@@ -24382,7 +24392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:17" ht="34">
       <c r="A30" s="285" t="s">
         <v>22</v>
       </c>
@@ -24435,7 +24445,7 @@
         <v>54.970999999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:17" ht="34">
       <c r="A31" s="285" t="s">
         <v>22</v>
       </c>
@@ -24486,7 +24496,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:17" ht="51">
       <c r="A32" s="285" t="s">
         <v>22</v>
       </c>
@@ -24539,7 +24549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:17" ht="51">
       <c r="A33" s="285" t="s">
         <v>22</v>
       </c>
@@ -24590,7 +24600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:17" ht="15.5" customHeight="1">
       <c r="A34" s="285" t="s">
         <v>22</v>
       </c>
@@ -24643,7 +24653,7 @@
         <v>61.427999999999997</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:17" ht="17">
       <c r="A35" s="285" t="s">
         <v>22</v>
       </c>
@@ -24694,7 +24704,7 @@
         <v>0.50600000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:17" ht="34">
       <c r="A36" s="285" t="s">
         <v>22</v>
       </c>
@@ -24745,7 +24755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:17" ht="34">
       <c r="A37" s="285" t="s">
         <v>22</v>
       </c>
@@ -24796,7 +24806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:17" ht="34">
       <c r="A38" s="285" t="s">
         <v>22</v>
       </c>
@@ -24847,7 +24857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:17" ht="34">
       <c r="A39" s="285" t="s">
         <v>22</v>
       </c>
@@ -24898,7 +24908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:17" ht="34">
       <c r="A40" s="285" t="s">
         <v>22</v>
       </c>
@@ -24949,7 +24959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:17" ht="34">
       <c r="A41" s="285" t="s">
         <v>22</v>
       </c>
@@ -25000,7 +25010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:17" ht="34">
       <c r="A42" s="285" t="s">
         <v>22</v>
       </c>
@@ -25051,7 +25061,7 @@
         <v>0.56799999999999995</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:17" ht="34">
       <c r="A43" s="285" t="s">
         <v>22</v>
       </c>
@@ -25102,7 +25112,7 @@
         <v>2.0000000000000002E-5</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:17" ht="17">
       <c r="A44" s="285" t="s">
         <v>24</v>
       </c>
@@ -25155,7 +25165,7 @@
         <v>227.6</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:17" ht="17">
       <c r="A45" s="285" t="s">
         <v>24</v>
       </c>
@@ -25208,7 +25218,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:17" ht="17">
       <c r="A46" s="285" t="s">
         <v>24</v>
       </c>
@@ -25261,7 +25271,7 @@
         <v>57.2</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:17" ht="17">
       <c r="A47" s="285" t="s">
         <v>24</v>
       </c>
@@ -25314,7 +25324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:17" ht="17">
       <c r="A48" s="285" t="s">
         <v>24</v>
       </c>
@@ -25367,7 +25377,7 @@
         <v>20.599999999999998</v>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:17" ht="17">
       <c r="A49" s="285" t="s">
         <v>24</v>
       </c>
@@ -25420,7 +25430,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:17" ht="17">
       <c r="A50" s="285" t="s">
         <v>24</v>
       </c>
@@ -25473,7 +25483,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:17" ht="17">
       <c r="A51" s="285" t="s">
         <v>24</v>
       </c>
@@ -25526,7 +25536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:17" ht="17">
       <c r="A52" s="285" t="s">
         <v>24</v>
       </c>
@@ -25579,7 +25589,7 @@
         <v>487.64000000000004</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:17" ht="17">
       <c r="A53" s="285" t="s">
         <v>24</v>
       </c>
@@ -25632,7 +25642,7 @@
         <v>33.85</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:17" ht="34">
       <c r="A54" s="285" t="s">
         <v>24</v>
       </c>
@@ -25685,7 +25695,7 @@
         <v>3.5499999999999997E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:17" ht="34">
       <c r="A55" s="285" t="s">
         <v>24</v>
       </c>
@@ -25738,7 +25748,7 @@
         <v>1.6000000000000001E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:17" ht="34">
       <c r="A56" s="285" t="s">
         <v>24</v>
       </c>
@@ -25791,7 +25801,7 @@
         <v>138.59200000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:17" ht="34">
       <c r="A57" s="285" t="s">
         <v>24</v>
       </c>
@@ -25844,7 +25854,7 @@
         <v>19.074999999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:17" ht="34">
       <c r="A58" s="285" t="s">
         <v>31</v>
       </c>
@@ -25879,7 +25889,7 @@
         <v>3384.1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:17" ht="34">
       <c r="A59" s="285" t="s">
         <v>31</v>
       </c>
@@ -25914,7 +25924,7 @@
         <v>146.06</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:17" ht="51">
       <c r="A60" s="285" t="s">
         <v>31</v>
       </c>
@@ -25951,7 +25961,7 @@
         <v>81.220000000000013</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:17" ht="51">
       <c r="A61" s="285" t="s">
         <v>31</v>
       </c>
@@ -25988,7 +25998,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:17" ht="68">
       <c r="A62" s="285" t="s">
         <v>31</v>
       </c>
@@ -26019,7 +26029,7 @@
         <v>22.26</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:17" ht="68">
       <c r="A63" s="285" t="s">
         <v>31</v>
       </c>
@@ -26048,7 +26058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:17" ht="51">
       <c r="A64" s="285" t="s">
         <v>33</v>
       </c>
@@ -26081,7 +26091,7 @@
         <v>1.1904189999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:17" ht="51">
       <c r="A65" s="285" t="s">
         <v>33</v>
       </c>
@@ -26112,7 +26122,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="76.900000000000006" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:17" ht="85">
       <c r="A66" s="285" t="s">
         <v>33</v>
       </c>
@@ -26141,7 +26151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="76.900000000000006" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:17" ht="85">
       <c r="A67" s="285" t="s">
         <v>33</v>
       </c>
@@ -26170,7 +26180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:17" ht="68">
       <c r="A68" s="285" t="s">
         <v>33</v>
       </c>
@@ -26201,7 +26211,7 @@
         <v>212.56641644999999</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:17" ht="68">
       <c r="A69" s="285" t="s">
         <v>33</v>
       </c>
@@ -26232,7 +26242,7 @@
         <v>266.62973053000002</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="76.900000000000006" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:17" ht="68">
       <c r="A70" s="285" t="s">
         <v>33</v>
       </c>
@@ -26267,7 +26277,7 @@
         <v>1.4429999999999998</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="76.900000000000006" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:17" ht="68">
       <c r="A71" s="285" t="s">
         <v>33</v>
       </c>
@@ -26300,7 +26310,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="62.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:17" ht="62.5" customHeight="1">
       <c r="A72" s="285" t="s">
         <v>33</v>
       </c>
@@ -26335,7 +26345,7 @@
         <v>0.1303</v>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="62.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:17" ht="62.5" customHeight="1">
       <c r="A73" s="285" t="s">
         <v>33</v>
       </c>
@@ -26368,7 +26378,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="169.15" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:17" ht="170">
       <c r="A74" s="285" t="s">
         <v>33</v>
       </c>
@@ -26401,7 +26411,7 @@
         <v>5.0927453000000007</v>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="169.15" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:17" ht="170">
       <c r="A75" s="285" t="s">
         <v>33</v>
       </c>
@@ -26430,7 +26440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="76.900000000000006" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:17" ht="85">
       <c r="A76" s="285" t="s">
         <v>33</v>
       </c>
@@ -26461,7 +26471,7 @@
         <v>0.17457500000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="76.900000000000006" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:17" ht="85">
       <c r="A77" s="285" t="s">
         <v>33</v>
       </c>
@@ -26490,7 +26500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:17" ht="68">
       <c r="A78" s="285" t="s">
         <v>33</v>
       </c>
@@ -26521,7 +26531,7 @@
         <v>0.68879100000000004</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:17" ht="68">
       <c r="A79" s="285" t="s">
         <v>33</v>
       </c>
@@ -26550,7 +26560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:17" ht="15.5" customHeight="1">
       <c r="A80" s="285" t="s">
         <v>42</v>
       </c>
@@ -26603,7 +26613,7 @@
         <v>1122.51</v>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:17" ht="17">
       <c r="A81" s="285" t="s">
         <v>42</v>
       </c>
@@ -26654,7 +26664,7 @@
         <v>161.52000000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:17" ht="15.5" customHeight="1">
       <c r="A82" s="285" t="s">
         <v>42</v>
       </c>
@@ -26685,7 +26695,7 @@
         <v>19.95</v>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:17" ht="17">
       <c r="A83" s="285" t="s">
         <v>42</v>
       </c>
@@ -26714,7 +26724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:17" ht="15.5" customHeight="1">
       <c r="A84" s="285" t="s">
         <v>42</v>
       </c>
@@ -26767,7 +26777,7 @@
         <v>457.59</v>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:17" ht="17">
       <c r="A85" s="285" t="s">
         <v>42</v>
       </c>
@@ -26818,7 +26828,7 @@
         <v>104.7</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:17" ht="34">
       <c r="A86" s="285" t="s">
         <v>45</v>
       </c>
@@ -26849,7 +26859,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:17" ht="34">
       <c r="A87" s="285" t="s">
         <v>45</v>
       </c>
@@ -26880,7 +26890,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:17" ht="34">
       <c r="A88" s="285" t="s">
         <v>45</v>
       </c>
@@ -26911,7 +26921,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:17" ht="34">
       <c r="A89" s="285" t="s">
         <v>45</v>
       </c>
@@ -26942,7 +26952,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:17" ht="15.5" customHeight="1">
       <c r="A90" s="285" t="s">
         <v>45</v>
       </c>
@@ -26973,7 +26983,7 @@
         <v>4.0000000000000002E-4</v>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:17" ht="17">
       <c r="A91" s="285" t="s">
         <v>45</v>
       </c>
@@ -27002,7 +27012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:17" ht="17">
       <c r="A92" s="285" t="s">
         <v>54</v>
       </c>
@@ -27035,7 +27045,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:17" ht="17">
       <c r="A93" s="285" t="s">
         <v>54</v>
       </c>
@@ -27066,7 +27076,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:17" ht="15.5" customHeight="1">
       <c r="A94" s="285" t="s">
         <v>54</v>
       </c>
@@ -27095,7 +27105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:17" ht="34">
       <c r="A95" s="285" t="s">
         <v>54</v>
       </c>
@@ -27126,7 +27136,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="31.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:17" ht="31.25" customHeight="1">
       <c r="A96" s="285" t="s">
         <v>54</v>
       </c>
@@ -27159,7 +27169,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="31.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:17" ht="31.25" customHeight="1">
       <c r="A97" s="285" t="s">
         <v>54</v>
       </c>
@@ -27188,7 +27198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:17" ht="15.5" customHeight="1">
       <c r="A98" s="285" t="s">
         <v>57</v>
       </c>
@@ -27223,7 +27233,7 @@
         <v>42068.35</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:17" ht="17">
       <c r="A99" s="285" t="s">
         <v>57</v>
       </c>
@@ -27256,7 +27266,7 @@
         <v>1257.26</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:17" ht="15.5" customHeight="1">
       <c r="A100" s="285" t="s">
         <v>57</v>
       </c>
@@ -27287,7 +27297,7 @@
         <v>10265.040000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:17" ht="17">
       <c r="A101" s="285" t="s">
         <v>57</v>
       </c>
@@ -27318,7 +27328,7 @@
         <v>3851.96</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:17" ht="17">
       <c r="A102" s="285" t="s">
         <v>57</v>
       </c>
@@ -27349,7 +27359,7 @@
         <v>1825.75</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:17" ht="17">
       <c r="A103" s="285" t="s">
         <v>57</v>
       </c>
@@ -27380,7 +27390,7 @@
         <v>408.5</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:17" ht="15.5" customHeight="1">
       <c r="A104" s="285" t="s">
         <v>57</v>
       </c>
@@ -27419,7 +27429,7 @@
         <v>28627.506687999998</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:17" ht="17">
       <c r="A105" s="285" t="s">
         <v>57</v>
       </c>
@@ -27470,7 +27480,7 @@
         <v>497.09999999999997</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:17" ht="15.5" customHeight="1">
       <c r="A106" s="285" t="s">
         <v>57</v>
       </c>
@@ -27509,7 +27519,7 @@
         <v>626.27167599999996</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:17" ht="17">
       <c r="A107" s="285" t="s">
         <v>57</v>
       </c>
@@ -27560,7 +27570,7 @@
         <v>5.8400000000000007</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:17" ht="15.5" customHeight="1">
       <c r="A108" s="285" t="s">
         <v>57</v>
       </c>
@@ -27591,7 +27601,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:17" ht="17">
       <c r="A109" s="285" t="s">
         <v>57</v>
       </c>
@@ -27622,7 +27632,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:17" ht="15.5" customHeight="1">
       <c r="A110" s="285" t="s">
         <v>57</v>
       </c>
@@ -27655,7 +27665,7 @@
         <v>284.89</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:17" ht="17">
       <c r="A111" s="285" t="s">
         <v>57</v>
       </c>
@@ -27686,7 +27696,7 @@
         <v>26.24</v>
       </c>
     </row>
-    <row r="112" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:17" ht="15.5" customHeight="1">
       <c r="A112" s="285" t="s">
         <v>57</v>
       </c>
@@ -27717,7 +27727,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:17" ht="17">
       <c r="A113" s="285" t="s">
         <v>57</v>
       </c>
@@ -27746,7 +27756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:17" ht="15.5" customHeight="1">
       <c r="A114" s="285" t="s">
         <v>57</v>
       </c>
@@ -27781,7 +27791,7 @@
         <v>0.45757999999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:17" ht="34">
       <c r="A115" s="285" t="s">
         <v>57</v>
       </c>
@@ -27814,7 +27824,7 @@
         <v>6.4020000000000006E-3</v>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:17" ht="15.5" customHeight="1">
       <c r="A116" s="285" t="s">
         <v>57</v>
       </c>
@@ -27845,7 +27855,7 @@
         <v>7.9399999999999991E-3</v>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:17" ht="51">
       <c r="A117" s="285" t="s">
         <v>57</v>
       </c>
@@ -27874,7 +27884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:17" ht="15.5" customHeight="1">
       <c r="A118" s="285" t="s">
         <v>57</v>
       </c>
@@ -27903,7 +27913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:17" ht="34">
       <c r="A119" s="285" t="s">
         <v>57</v>
       </c>
@@ -27932,7 +27942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:17" ht="15.5" customHeight="1">
       <c r="A120" s="285" t="s">
         <v>57</v>
       </c>
@@ -27961,7 +27971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:17" ht="17">
       <c r="A121" s="285" t="s">
         <v>57</v>
       </c>
@@ -27990,7 +28000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:17" ht="31.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:17" ht="31.25" customHeight="1">
       <c r="A122" s="285" t="s">
         <v>57</v>
       </c>
@@ -28021,7 +28031,7 @@
         <v>1.01E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:17" ht="31.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:17" ht="31.25" customHeight="1">
       <c r="A123" s="285" t="s">
         <v>57</v>
       </c>
@@ -28052,7 +28062,7 @@
         <v>8.0999999999999996E-3</v>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:17" ht="17">
       <c r="A124" s="285" t="s">
         <v>57</v>
       </c>
@@ -28083,7 +28093,7 @@
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:17" ht="17">
       <c r="A125" s="285" t="s">
         <v>57</v>
       </c>
@@ -28112,7 +28122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:17" ht="17">
       <c r="A126" s="285" t="s">
         <v>68</v>
       </c>
@@ -28143,7 +28153,7 @@
         <v>920.05</v>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:17" ht="17">
       <c r="A127" s="285" t="s">
         <v>68</v>
       </c>
@@ -28174,7 +28184,7 @@
         <v>361.74</v>
       </c>
     </row>
-    <row r="128" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:17" ht="15.5" customHeight="1">
       <c r="A128" s="285" t="s">
         <v>68</v>
       </c>
@@ -28205,7 +28215,7 @@
         <v>18.809999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:17" ht="17">
       <c r="A129" s="285" t="s">
         <v>68</v>
       </c>
@@ -28234,7 +28244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:17" ht="15.5" customHeight="1">
       <c r="A130" s="285" t="s">
         <v>72</v>
       </c>
@@ -28265,7 +28275,7 @@
         <v>240.3</v>
       </c>
     </row>
-    <row r="131" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:17" ht="17">
       <c r="A131" s="285" t="s">
         <v>72</v>
       </c>
@@ -28298,7 +28308,7 @@
         <v>63.9</v>
       </c>
     </row>
-    <row r="132" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:17" ht="15.5" customHeight="1">
       <c r="A132" s="285" t="s">
         <v>72</v>
       </c>
@@ -28329,7 +28339,7 @@
         <v>68.400000000000006</v>
       </c>
     </row>
-    <row r="133" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:17" ht="34">
       <c r="A133" s="285" t="s">
         <v>72</v>
       </c>
@@ -28362,7 +28372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:17" ht="15.5" customHeight="1">
       <c r="A134" s="285" t="s">
         <v>73</v>
       </c>
@@ -28409,7 +28419,7 @@
         <v>57.961036038617792</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:17" ht="17">
       <c r="A135" s="285" t="s">
         <v>73</v>
       </c>
@@ -28444,7 +28454,7 @@
         <v>12.638026223480253</v>
       </c>
     </row>
-    <row r="136" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:17" ht="15.5" customHeight="1">
       <c r="A136" s="285" t="s">
         <v>73</v>
       </c>
@@ -28487,7 +28497,7 @@
         <v>2.9407796400000001</v>
       </c>
     </row>
-    <row r="137" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:17" ht="17">
       <c r="A137" s="285" t="s">
         <v>73</v>
       </c>
@@ -28518,7 +28528,7 @@
         <v>1.3539460000000001</v>
       </c>
     </row>
-    <row r="138" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:17" ht="15.5" customHeight="1">
       <c r="A138" s="285" t="s">
         <v>76</v>
       </c>
@@ -28549,7 +28559,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="139" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:17" ht="34">
       <c r="A139" s="285" t="s">
         <v>76</v>
       </c>
@@ -28580,7 +28590,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="140" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:17" ht="34">
       <c r="A140" s="285" t="s">
         <v>76</v>
       </c>
@@ -28613,7 +28623,7 @@
         <v>848.08</v>
       </c>
     </row>
-    <row r="141" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:17" ht="34">
       <c r="A141" s="285" t="s">
         <v>76</v>
       </c>
@@ -28642,7 +28652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:17" ht="15.5" customHeight="1">
       <c r="A142" s="285" t="s">
         <v>76</v>
       </c>
@@ -28675,7 +28685,7 @@
         <v>158.20000000000002</v>
       </c>
     </row>
-    <row r="143" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:17" ht="34">
       <c r="A143" s="285" t="s">
         <v>76</v>
       </c>
@@ -28704,7 +28714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:17" ht="15.5" customHeight="1">
       <c r="A144" s="285" t="s">
         <v>76</v>
       </c>
@@ -28735,7 +28745,7 @@
         <v>24.490000000000002</v>
       </c>
     </row>
-    <row r="145" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:17" ht="34">
       <c r="A145" s="285" t="s">
         <v>76</v>
       </c>
@@ -28766,7 +28776,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="146" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:17" ht="34">
       <c r="A146" s="285" t="s">
         <v>76</v>
       </c>
@@ -28799,7 +28809,7 @@
         <v>14.26</v>
       </c>
     </row>
-    <row r="147" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:17" ht="34">
       <c r="A147" s="285" t="s">
         <v>76</v>
       </c>
@@ -28828,7 +28838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:17" ht="34">
       <c r="A148" s="285" t="s">
         <v>76</v>
       </c>
@@ -28859,7 +28869,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="149" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:17" ht="34">
       <c r="A149" s="285" t="s">
         <v>76</v>
       </c>
@@ -28888,7 +28898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:17" ht="34">
       <c r="A150" s="285" t="s">
         <v>76</v>
       </c>
@@ -28921,7 +28931,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="151" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:17" ht="34">
       <c r="A151" s="285" t="s">
         <v>76</v>
       </c>
@@ -28952,7 +28962,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="152" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:17" ht="34">
       <c r="A152" s="285" t="s">
         <v>76</v>
       </c>
@@ -28983,7 +28993,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="153" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:17" ht="34">
       <c r="A153" s="285" t="s">
         <v>76</v>
       </c>
@@ -29014,7 +29024,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="154" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:17" ht="51">
       <c r="A154" s="285" t="s">
         <v>76</v>
       </c>
@@ -29045,7 +29055,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="155" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:17" ht="51">
       <c r="A155" s="285" t="s">
         <v>76</v>
       </c>
@@ -29074,7 +29084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:17" ht="17">
       <c r="A156" s="285" t="s">
         <v>82</v>
       </c>
@@ -29127,7 +29137,7 @@
         <v>4566</v>
       </c>
     </row>
-    <row r="157" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:17" ht="17">
       <c r="A157" s="285" t="s">
         <v>82</v>
       </c>
@@ -29178,7 +29188,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="158" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:17" ht="17">
       <c r="A158" s="285" t="s">
         <v>82</v>
       </c>
@@ -29231,7 +29241,7 @@
         <v>3925</v>
       </c>
     </row>
-    <row r="159" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:17" ht="17">
       <c r="A159" s="285" t="s">
         <v>82</v>
       </c>
@@ -29282,7 +29292,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="160" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:17" ht="51">
       <c r="A160" s="285" t="s">
         <v>82</v>
       </c>
@@ -29335,7 +29345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:17" ht="51">
       <c r="A161" s="285" t="s">
         <v>82</v>
       </c>
@@ -29386,7 +29396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:17" ht="34">
       <c r="A162" s="285" t="s">
         <v>85</v>
       </c>
@@ -29421,7 +29431,7 @@
         <v>15600</v>
       </c>
     </row>
-    <row r="163" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:17" ht="34">
       <c r="A163" s="285" t="s">
         <v>85</v>
       </c>
@@ -29452,7 +29462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:17" ht="15.5" customHeight="1">
       <c r="A164" s="285" t="s">
         <v>87</v>
       </c>
@@ -29483,7 +29493,7 @@
         <v>2078.81</v>
       </c>
     </row>
-    <row r="165" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:17" ht="51">
       <c r="A165" s="285" t="s">
         <v>87</v>
       </c>
@@ -29514,7 +29524,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="166" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:17" ht="15.5" customHeight="1">
       <c r="A166" s="285" t="s">
         <v>87</v>
       </c>
@@ -29545,7 +29555,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="167" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:17" ht="51">
       <c r="A167" s="285" t="s">
         <v>87</v>
       </c>
@@ -29576,7 +29586,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="168" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:17" ht="34">
       <c r="A168" s="285" t="s">
         <v>87</v>
       </c>
@@ -29607,7 +29617,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="169" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:17" ht="34">
       <c r="A169" s="285" t="s">
         <v>87</v>
       </c>
@@ -29638,7 +29648,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="170" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:17" ht="68">
       <c r="A170" s="285" t="s">
         <v>87</v>
       </c>
@@ -29669,7 +29679,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="171" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:17" ht="68">
       <c r="A171" s="285" t="s">
         <v>87</v>
       </c>
@@ -29700,7 +29710,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="172" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:17" ht="51">
       <c r="A172" s="285" t="s">
         <v>87</v>
       </c>
@@ -29729,7 +29739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:17" ht="51">
       <c r="A173" s="285" t="s">
         <v>87</v>
       </c>
@@ -29758,7 +29768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:17" ht="51">
       <c r="A174" s="285" t="s">
         <v>87</v>
       </c>
@@ -29793,7 +29803,7 @@
         <v>97.6</v>
       </c>
     </row>
-    <row r="175" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:17" ht="51">
       <c r="A175" s="285" t="s">
         <v>87</v>
       </c>
@@ -29824,7 +29834,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="176" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:17" ht="51">
       <c r="A176" s="285" t="s">
         <v>87</v>
       </c>
@@ -29857,7 +29867,7 @@
         <v>3.8000000000000003</v>
       </c>
     </row>
-    <row r="177" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:17" ht="51">
       <c r="A177" s="285" t="s">
         <v>87</v>
       </c>
@@ -29888,7 +29898,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="178" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:17" ht="68">
       <c r="A178" s="285" t="s">
         <v>87</v>
       </c>
@@ -29921,7 +29931,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="179" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:17" ht="68">
       <c r="A179" s="285" t="s">
         <v>87</v>
       </c>
@@ -29952,7 +29962,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="180" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:17" ht="51">
       <c r="A180" s="285" t="s">
         <v>87</v>
       </c>
@@ -29991,7 +30001,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="181" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:17" ht="51">
       <c r="A181" s="285" t="s">
         <v>87</v>
       </c>
@@ -30022,7 +30032,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="182" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:17" ht="51">
       <c r="A182" s="285" t="s">
         <v>87</v>
       </c>
@@ -30053,7 +30063,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="183" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:17" ht="51">
       <c r="A183" s="285" t="s">
         <v>87</v>
       </c>
@@ -30084,7 +30094,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="184" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:17" ht="34">
       <c r="A184" s="285" t="s">
         <v>87</v>
       </c>
@@ -30117,7 +30127,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="185" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:17" ht="34">
       <c r="A185" s="285" t="s">
         <v>87</v>
       </c>
@@ -30148,7 +30158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:17" ht="68">
       <c r="A186" s="285" t="s">
         <v>87</v>
       </c>
@@ -30185,7 +30195,7 @@
         <v>289.41000000000003</v>
       </c>
     </row>
-    <row r="187" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:17" ht="68">
       <c r="A187" s="285" t="s">
         <v>87</v>
       </c>
@@ -30218,7 +30228,7 @@
         <v>12.739999999999998</v>
       </c>
     </row>
-    <row r="188" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:17" ht="68">
       <c r="A188" s="285" t="s">
         <v>87</v>
       </c>
@@ -30251,7 +30261,7 @@
         <v>467.78999999999996</v>
       </c>
     </row>
-    <row r="189" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:17" ht="68">
       <c r="A189" s="285" t="s">
         <v>87</v>
       </c>
@@ -30280,7 +30290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:17" ht="68">
       <c r="A190" s="285" t="s">
         <v>87</v>
       </c>
@@ -30311,7 +30321,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="191" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:17" ht="68">
       <c r="A191" s="285" t="s">
         <v>87</v>
       </c>
@@ -30340,7 +30350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:17" ht="68">
       <c r="A192" s="285" t="s">
         <v>87</v>
       </c>
@@ -30371,7 +30381,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="193" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:17" ht="68">
       <c r="A193" s="285" t="s">
         <v>87</v>
       </c>
@@ -30400,7 +30410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:17" ht="31.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:17" ht="31.25" customHeight="1">
       <c r="A194" s="285" t="s">
         <v>87</v>
       </c>
@@ -30429,7 +30439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:17" ht="31.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:17" ht="31.25" customHeight="1">
       <c r="A195" s="285" t="s">
         <v>87</v>
       </c>
@@ -30458,7 +30468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:17" ht="51">
       <c r="A196" s="285" t="s">
         <v>87</v>
       </c>
@@ -30487,7 +30497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:17" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:17" ht="51">
       <c r="A197" s="285" t="s">
         <v>87</v>
       </c>
@@ -30516,7 +30526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:17" ht="68">
       <c r="A198" s="285" t="s">
         <v>87</v>
       </c>
@@ -30545,7 +30555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:17" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:17" ht="68">
       <c r="A199" s="285" t="s">
         <v>87</v>
       </c>
@@ -30574,7 +30584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:17" ht="17">
       <c r="A200" s="285" t="s">
         <v>88</v>
       </c>
@@ -30611,7 +30621,7 @@
         <v>48.5</v>
       </c>
     </row>
-    <row r="201" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:17" ht="17">
       <c r="A201" s="285" t="s">
         <v>88</v>
       </c>
@@ -30642,7 +30652,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="202" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:17" ht="17">
       <c r="A202" s="285" t="s">
         <v>88</v>
       </c>
@@ -30677,7 +30687,7 @@
         <v>26.48</v>
       </c>
     </row>
-    <row r="203" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:17" ht="17">
       <c r="A203" s="285" t="s">
         <v>88</v>
       </c>
@@ -30708,7 +30718,7 @@
         <v>12.27</v>
       </c>
     </row>
-    <row r="204" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:17" ht="17">
       <c r="A204" s="285" t="s">
         <v>88</v>
       </c>
@@ -30745,7 +30755,7 @@
         <v>2096.2500000000005</v>
       </c>
     </row>
-    <row r="205" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:17" ht="17">
       <c r="A205" s="285" t="s">
         <v>88</v>
       </c>
@@ -30776,7 +30786,7 @@
         <v>46.44</v>
       </c>
     </row>
-    <row r="206" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:17" ht="34">
       <c r="A206" s="285" t="s">
         <v>88</v>
       </c>
@@ -30811,7 +30821,7 @@
         <v>868.98400000000004</v>
       </c>
     </row>
-    <row r="207" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:17" ht="34">
       <c r="A207" s="285" t="s">
         <v>88</v>
       </c>
@@ -30842,7 +30852,7 @@
         <v>6.1440000000000001</v>
       </c>
     </row>
-    <row r="208" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:17" ht="34">
       <c r="A208" s="285" t="s">
         <v>88</v>
       </c>
@@ -30879,7 +30889,7 @@
         <v>20.905999999999999</v>
       </c>
     </row>
-    <row r="209" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:17" ht="34">
       <c r="A209" s="285" t="s">
         <v>88</v>
       </c>
@@ -30914,7 +30924,7 @@
         <v>0.8600000000000001</v>
       </c>
     </row>
-    <row r="210" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:17" ht="15.5" customHeight="1">
       <c r="A210" s="285" t="s">
         <v>88</v>
       </c>
@@ -30947,7 +30957,7 @@
         <v>32.44</v>
       </c>
     </row>
-    <row r="211" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:17" ht="17">
       <c r="A211" s="285" t="s">
         <v>88</v>
       </c>
@@ -30976,7 +30986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:17" ht="15.5" customHeight="1">
       <c r="A212" s="285" t="s">
         <v>88</v>
       </c>
@@ -31007,7 +31017,7 @@
         <v>713.72</v>
       </c>
     </row>
-    <row r="213" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:17" ht="17">
       <c r="A213" s="285" t="s">
         <v>88</v>
       </c>
@@ -31038,7 +31048,7 @@
         <v>647.63</v>
       </c>
     </row>
-    <row r="214" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:17" ht="17">
       <c r="A214" s="285" t="s">
         <v>88</v>
       </c>
@@ -31083,7 +31093,7 @@
         <v>232.7</v>
       </c>
     </row>
-    <row r="215" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:17" ht="17">
       <c r="A215" s="285" t="s">
         <v>88</v>
       </c>
@@ -31116,7 +31126,7 @@
         <v>31.490000000000002</v>
       </c>
     </row>
-    <row r="216" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:17" ht="17">
       <c r="A216" s="285" t="s">
         <v>88</v>
       </c>
@@ -31147,7 +31157,7 @@
         <v>11.19</v>
       </c>
     </row>
-    <row r="217" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:17" ht="17">
       <c r="A217" s="285" t="s">
         <v>88</v>
       </c>
@@ -31178,7 +31188,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:17" ht="34">
       <c r="A218" s="285" t="s">
         <v>88</v>
       </c>
@@ -31209,7 +31219,7 @@
         <v>125.59</v>
       </c>
     </row>
-    <row r="219" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:17" ht="34">
       <c r="A219" s="285" t="s">
         <v>88</v>
       </c>
@@ -31240,7 +31250,7 @@
         <v>9.4600000000000009</v>
       </c>
     </row>
-    <row r="220" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:17" ht="34">
       <c r="A220" s="285" t="s">
         <v>88</v>
       </c>
@@ -31271,7 +31281,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="221" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:17" ht="34">
       <c r="A221" s="285" t="s">
         <v>88</v>
       </c>
@@ -31302,7 +31312,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="222" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:17" ht="34">
       <c r="A222" s="285" t="s">
         <v>88</v>
       </c>
@@ -31333,7 +31343,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="223" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:17" ht="34">
       <c r="A223" s="285" t="s">
         <v>88</v>
       </c>
@@ -31364,7 +31374,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="224" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:17" ht="34">
       <c r="A224" s="285" t="s">
         <v>88</v>
       </c>
@@ -31397,7 +31407,7 @@
         <v>1.5580000000000001</v>
       </c>
     </row>
-    <row r="225" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:17" ht="34">
       <c r="A225" s="285" t="s">
         <v>88</v>
       </c>
@@ -31426,7 +31436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:17" ht="17">
       <c r="A226" s="285" t="s">
         <v>88</v>
       </c>
@@ -31457,7 +31467,7 @@
         <v>29.59</v>
       </c>
     </row>
-    <row r="227" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:17" ht="17">
       <c r="A227" s="285" t="s">
         <v>88</v>
       </c>
@@ -31488,7 +31498,7 @@
         <v>8.8699999999999992</v>
       </c>
     </row>
-    <row r="228" spans="1:17" s="341" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:17" s="341" customFormat="1">
       <c r="A228" s="334"/>
       <c r="B228" s="335"/>
       <c r="C228" s="336"/>
@@ -31507,7 +31517,7 @@
       <c r="P228" s="339"/>
       <c r="Q228" s="340"/>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:17">
       <c r="A229" s="236"/>
       <c r="B229" s="236"/>
       <c r="C229" s="236"/>
@@ -31526,7 +31536,7 @@
       <c r="P229" s="237"/>
       <c r="Q229" s="237"/>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:17">
       <c r="A230" s="102"/>
       <c r="B230" s="102"/>
       <c r="C230" s="102"/>
@@ -31545,7 +31555,7 @@
       <c r="P230" s="24"/>
       <c r="Q230" s="24"/>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:17">
       <c r="A231" s="102"/>
       <c r="B231" s="102"/>
       <c r="C231" s="102"/>
@@ -31563,11 +31573,11 @@
       <c r="O231" s="102"/>
       <c r="P231" s="102"/>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:17">
       <c r="M232" s="25"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q228"/>
+  <autoFilter ref="A3:Q228" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
@@ -31582,39 +31592,39 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AG32"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.86328125" style="75" customWidth="1"/>
-    <col min="2" max="2" width="17.1328125" style="75" customWidth="1"/>
-    <col min="3" max="4" width="14.1328125" style="75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.46484375" style="75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.83203125" style="75" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" style="75" customWidth="1"/>
+    <col min="3" max="4" width="14.1640625" style="75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5" style="75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.6640625" style="75" customWidth="1"/>
     <col min="7" max="7" width="7.33203125" style="75" customWidth="1"/>
-    <col min="8" max="9" width="12.46484375" style="75" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.5" style="75" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.33203125" style="75" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="3.1328125" style="75" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="3.1640625" style="75" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.6640625" style="75" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.46484375" style="75" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="8.46484375" style="75" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="6.53125" style="75" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.46484375" style="75" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="3.1328125" style="75" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.46484375" style="75" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5" style="75" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="8.5" style="75" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="6.5" style="75" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.5" style="75" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="3.1640625" style="75" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.5" style="75" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="12" style="75" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.1328125" style="75" customWidth="1"/>
+    <col min="25" max="25" width="9.1640625" style="75" customWidth="1"/>
     <col min="26" max="27" width="7" style="75" customWidth="1"/>
     <col min="28" max="28" width="16.33203125" style="75" customWidth="1"/>
     <col min="29" max="29" width="13.6640625" style="75" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="2.53125" style="75" customWidth="1"/>
-    <col min="31" max="31" width="3.86328125" style="75" customWidth="1"/>
-    <col min="32" max="32" width="15.1328125" style="75" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.1328125" style="75" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.1328125" style="75"/>
+    <col min="30" max="30" width="2.5" style="75" customWidth="1"/>
+    <col min="31" max="31" width="3.83203125" style="75" customWidth="1"/>
+    <col min="32" max="32" width="15.1640625" style="75" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1640625" style="75" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.1640625" style="75"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:33">
       <c r="B1" s="377" t="s">
         <v>467</v>
       </c>
@@ -31650,7 +31660,7 @@
       <c r="AF1" s="377"/>
       <c r="AG1" s="377"/>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:33">
       <c r="B2" s="378" t="s">
         <v>152</v>
       </c>
@@ -31686,7 +31696,7 @@
       <c r="AF2" s="378"/>
       <c r="AG2" s="378"/>
     </row>
-    <row r="3" spans="1:33" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:33" ht="16" thickBot="1">
       <c r="B3" s="379" t="s">
         <v>116</v>
       </c>
@@ -31722,7 +31732,7 @@
       <c r="AF3" s="379"/>
       <c r="AG3" s="379"/>
     </row>
-    <row r="4" spans="1:33" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:33" ht="16" thickBot="1">
       <c r="A4" s="76"/>
       <c r="B4" s="76"/>
       <c r="C4" s="381" t="s">
@@ -31761,7 +31771,7 @@
       </c>
       <c r="AG4" s="385"/>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:33">
       <c r="A5" s="77"/>
       <c r="B5" s="108"/>
       <c r="C5" s="372" t="s">
@@ -31808,7 +31818,7 @@
       <c r="AF5" s="386"/>
       <c r="AG5" s="387"/>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:33">
       <c r="A6" s="77"/>
       <c r="B6" s="108"/>
       <c r="C6" s="374"/>
@@ -31843,7 +31853,7 @@
       <c r="AF6" s="386"/>
       <c r="AG6" s="387"/>
     </row>
-    <row r="7" spans="1:33" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:33" ht="57.75" customHeight="1">
       <c r="A7" s="244" t="s">
         <v>7</v>
       </c>
@@ -31944,7 +31954,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:33" ht="30">
       <c r="A8" s="343" t="s">
         <v>31</v>
       </c>
@@ -32001,7 +32011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:33">
       <c r="A9" s="343" t="s">
         <v>42</v>
       </c>
@@ -32052,7 +32062,7 @@
         <v>12.891</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:33" ht="30">
       <c r="A10" s="343" t="s">
         <v>57</v>
       </c>
@@ -32099,7 +32109,7 @@
         <v>30.68</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:33" ht="30">
       <c r="A11" s="343" t="s">
         <v>57</v>
       </c>
@@ -32152,7 +32162,7 @@
       <c r="AF11" s="343"/>
       <c r="AG11" s="343"/>
     </row>
-    <row r="12" spans="1:33" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:33" ht="30">
       <c r="A12" s="343" t="s">
         <v>57</v>
       </c>
@@ -32205,7 +32215,7 @@
       <c r="AF12" s="343"/>
       <c r="AG12" s="343"/>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:33">
       <c r="A13" s="343" t="s">
         <v>57</v>
       </c>
@@ -32252,7 +32262,7 @@
         <v>11554.3</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:33">
       <c r="A14" s="343" t="s">
         <v>57</v>
       </c>
@@ -32299,7 +32309,7 @@
         <v>648.84</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:33" ht="30">
       <c r="A15" s="343" t="s">
         <v>57</v>
       </c>
@@ -32342,7 +32352,7 @@
       <c r="AF15" s="343"/>
       <c r="AG15" s="343"/>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:33">
       <c r="A16" s="343" t="s">
         <v>57</v>
       </c>
@@ -32389,7 +32399,7 @@
         <v>11.57</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:33" ht="30">
       <c r="A17" s="343" t="s">
         <v>57</v>
       </c>
@@ -32442,7 +32452,7 @@
       <c r="AF17" s="343"/>
       <c r="AG17" s="343"/>
     </row>
-    <row r="18" spans="1:33" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:33" ht="30">
       <c r="A18" s="343" t="s">
         <v>57</v>
       </c>
@@ -32485,7 +32495,7 @@
       <c r="AF18" s="343"/>
       <c r="AG18" s="343"/>
     </row>
-    <row r="19" spans="1:33" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:33" ht="30">
       <c r="A19" s="343" t="s">
         <v>57</v>
       </c>
@@ -32532,7 +32542,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:33" ht="30">
       <c r="A20" s="343" t="s">
         <v>57</v>
       </c>
@@ -32579,7 +32589,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:33" ht="45">
       <c r="A21" s="343" t="s">
         <v>57</v>
       </c>
@@ -32626,7 +32636,7 @@
         <v>8.23</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:33" ht="45">
       <c r="A22" s="343" t="s">
         <v>57</v>
       </c>
@@ -32671,7 +32681,7 @@
       <c r="AF22" s="343"/>
       <c r="AG22" s="343"/>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:33">
       <c r="A23" s="343" t="s">
         <v>82</v>
       </c>
@@ -32724,7 +32734,7 @@
       <c r="AF23" s="343"/>
       <c r="AG23" s="343"/>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:33">
       <c r="A24" s="343" t="s">
         <v>82</v>
       </c>
@@ -32777,7 +32787,7 @@
       <c r="AF24" s="343"/>
       <c r="AG24" s="343"/>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:33">
       <c r="A25" s="343" t="s">
         <v>85</v>
       </c>
@@ -32838,7 +32848,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:33" ht="30">
       <c r="A26" s="343" t="s">
         <v>87</v>
       </c>
@@ -32897,7 +32907,7 @@
       <c r="AF26" s="343"/>
       <c r="AG26" s="343"/>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:33" ht="16">
       <c r="A27" s="247"/>
       <c r="B27" s="247" t="s">
         <v>118</v>
@@ -32962,12 +32972,12 @@
         <v>12255.599999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:33">
       <c r="AG32" s="160"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:AG26">
-    <sortState ref="A8:AG27">
+  <autoFilter ref="A7:AG26" xr:uid="{00000000-0009-0000-0000-000005000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:AG27">
       <sortCondition ref="A7:A26"/>
     </sortState>
   </autoFilter>
@@ -32996,28 +33006,28 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A2:P35"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="27" customWidth="1"/>
     <col min="2" max="3" width="10.33203125" style="27" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="9.6640625" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.1328125" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1328125" style="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.86328125" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.83203125" style="27" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="27" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="9.6640625" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.46484375" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.46484375" style="30" customWidth="1"/>
-    <col min="15" max="16" width="14.1328125" style="27" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.1328125" style="27"/>
+    <col min="12" max="12" width="13.5" style="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.5" style="30" customWidth="1"/>
+    <col min="15" max="16" width="14.1640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.1640625" style="27"/>
     <col min="18" max="18" width="11.33203125" style="27" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="27"/>
+    <col min="19" max="16384" width="9.1640625" style="27"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" ht="16">
       <c r="A2" s="390" t="s">
         <v>510</v>
       </c>
@@ -33037,7 +33047,7 @@
       <c r="O2" s="390"/>
       <c r="P2" s="390"/>
     </row>
-    <row r="3" spans="1:16" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" ht="16">
       <c r="A3" s="391" t="s">
         <v>116</v>
       </c>
@@ -33057,7 +33067,7 @@
       <c r="O3" s="391"/>
       <c r="P3" s="391"/>
     </row>
-    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" ht="16">
       <c r="A4" s="28"/>
       <c r="B4" s="392" t="s">
         <v>142</v>
@@ -33079,7 +33089,7 @@
       </c>
       <c r="P4" s="393"/>
     </row>
-    <row r="5" spans="1:16" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" ht="16">
       <c r="A5" s="28"/>
       <c r="B5" s="392" t="s">
         <v>144</v>
@@ -33109,7 +33119,7 @@
       <c r="O5" s="393"/>
       <c r="P5" s="393"/>
     </row>
-    <row r="6" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" ht="29.25" customHeight="1">
       <c r="A6" s="28"/>
       <c r="B6" s="392"/>
       <c r="C6" s="393"/>
@@ -33127,7 +33137,7 @@
       <c r="O6" s="393"/>
       <c r="P6" s="393"/>
     </row>
-    <row r="7" spans="1:16" ht="74.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" ht="74.25" customHeight="1">
       <c r="A7" s="71" t="s">
         <v>7</v>
       </c>
@@ -33175,7 +33185,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" ht="16">
       <c r="A8" s="342" t="s">
         <v>22</v>
       </c>
@@ -33223,7 +33233,7 @@
         <v>4.1690000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" ht="16">
       <c r="A9" s="342" t="s">
         <v>23</v>
       </c>
@@ -33271,7 +33281,7 @@
         <v>6.8929999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" ht="16">
       <c r="A10" s="346" t="s">
         <v>24</v>
       </c>
@@ -33319,7 +33329,7 @@
         <v>952.82999999999993</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" ht="16">
       <c r="A11" s="342" t="s">
         <v>103</v>
       </c>
@@ -33367,7 +33377,7 @@
         <v>20.309999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" ht="16">
       <c r="A12" s="342" t="s">
         <v>27</v>
       </c>
@@ -33415,7 +33425,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" ht="16">
       <c r="A13" s="342" t="s">
         <v>29</v>
       </c>
@@ -33463,7 +33473,7 @@
         <v>7.0850655299999996</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" ht="16">
       <c r="A14" s="342" t="s">
         <v>31</v>
       </c>
@@ -33511,7 +33521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" ht="16">
       <c r="A15" s="342" t="s">
         <v>33</v>
       </c>
@@ -33559,7 +33569,7 @@
         <v>4.3587893099999997</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:16" ht="16">
       <c r="A16" s="342" t="s">
         <v>42</v>
       </c>
@@ -33607,7 +33617,7 @@
         <v>14.690000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:16" ht="16">
       <c r="A17" s="342" t="s">
         <v>45</v>
       </c>
@@ -33655,7 +33665,7 @@
         <v>13.515000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:16" ht="16">
       <c r="A18" s="342" t="s">
         <v>49</v>
       </c>
@@ -33703,7 +33713,7 @@
         <v>38.449999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:16" ht="16">
       <c r="A19" s="346" t="s">
         <v>54</v>
       </c>
@@ -33751,7 +33761,7 @@
         <v>34.04</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:16" ht="16">
       <c r="A20" s="342" t="s">
         <v>57</v>
       </c>
@@ -33799,7 +33809,7 @@
         <v>12256.699999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:16" ht="16">
       <c r="A21" s="342" t="s">
         <v>68</v>
       </c>
@@ -33847,7 +33857,7 @@
         <v>482.26256799999993</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:16" ht="16">
       <c r="A22" s="342" t="s">
         <v>70</v>
       </c>
@@ -33895,7 +33905,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:16" ht="16">
       <c r="A23" s="342" t="s">
         <v>102</v>
       </c>
@@ -33943,7 +33953,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:16" ht="16">
       <c r="A24" s="342" t="s">
         <v>71</v>
       </c>
@@ -33991,7 +34001,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:16" ht="16">
       <c r="A25" s="342" t="s">
         <v>72</v>
       </c>
@@ -34039,7 +34049,7 @@
         <v>246.9</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:16" ht="16">
       <c r="A26" s="342" t="s">
         <v>73</v>
       </c>
@@ -34087,7 +34097,7 @@
         <v>65.099999999999994</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:16" ht="16">
       <c r="A27" s="342" t="s">
         <v>76</v>
       </c>
@@ -34135,7 +34145,7 @@
         <v>5.1999999999999998E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:16" ht="16">
       <c r="A28" s="342" t="s">
         <v>82</v>
       </c>
@@ -34183,7 +34193,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:16" ht="16">
       <c r="A29" s="342" t="s">
         <v>112</v>
       </c>
@@ -34231,7 +34241,7 @@
         <v>14.495900000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:16" ht="16">
       <c r="A30" s="342" t="s">
         <v>85</v>
       </c>
@@ -34279,7 +34289,7 @@
         <v>1.3839999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:16" ht="16">
       <c r="A31" s="342" t="s">
         <v>86</v>
       </c>
@@ -34327,7 +34337,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:16" ht="16">
       <c r="A32" s="342" t="s">
         <v>87</v>
       </c>
@@ -34375,7 +34385,7 @@
         <v>382.32</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:16" ht="16">
       <c r="A33" s="342" t="s">
         <v>88</v>
       </c>
@@ -34423,7 +34433,7 @@
         <v>22.630000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:16">
       <c r="B35" s="161"/>
       <c r="C35" s="161"/>
       <c r="D35" s="161"/>
@@ -34465,26 +34475,26 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:Q97"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="37" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.53125" style="37" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.46484375" style="37" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.5" style="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="37" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="16" style="37" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.46484375" style="37" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" style="37" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="16" style="37" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.46484375" style="37" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="37" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="16" style="37" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.46484375" style="37" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5" style="37" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="16" style="37" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.46484375" style="37" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5" style="37" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="16" style="37" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.1328125" style="37"/>
+    <col min="18" max="16384" width="9.1640625" style="37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17" ht="16">
       <c r="B1" s="395"/>
       <c r="C1" s="395"/>
       <c r="D1" s="395"/>
@@ -34502,7 +34512,7 @@
       <c r="P1" s="395"/>
       <c r="Q1" s="395"/>
     </row>
-    <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:17" ht="16">
       <c r="B2" s="396" t="s">
         <v>509</v>
       </c>
@@ -34522,7 +34532,7 @@
       <c r="P2" s="396"/>
       <c r="Q2" s="396"/>
     </row>
-    <row r="3" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" ht="16">
       <c r="B3" s="397"/>
       <c r="C3" s="397"/>
       <c r="D3" s="397"/>
@@ -34540,7 +34550,7 @@
       <c r="P3" s="397"/>
       <c r="Q3" s="397"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="255"/>
       <c r="B4" s="256"/>
       <c r="C4" s="398"/>
@@ -34559,7 +34569,7 @@
       <c r="P4" s="399"/>
       <c r="Q4" s="399"/>
     </row>
-    <row r="5" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17" ht="16">
       <c r="A5" s="257"/>
       <c r="B5" s="258"/>
       <c r="C5" s="401" t="s">
@@ -34588,7 +34598,7 @@
       <c r="P5" s="401"/>
       <c r="Q5" s="402"/>
     </row>
-    <row r="6" spans="1:17" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:17" ht="17.25" customHeight="1" thickBot="1">
       <c r="A6" s="259"/>
       <c r="B6" s="260"/>
       <c r="C6" s="404"/>
@@ -34607,7 +34617,7 @@
       <c r="P6" s="404"/>
       <c r="Q6" s="405"/>
     </row>
-    <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" ht="51" customHeight="1">
       <c r="A7" s="254" t="s">
         <v>7</v>
       </c>
@@ -34660,7 +34670,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A8" s="351" t="s">
         <v>22</v>
       </c>
@@ -34695,7 +34705,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A9" s="351" t="s">
         <v>23</v>
       </c>
@@ -34726,7 +34736,7 @@
       <c r="P9" s="353"/>
       <c r="Q9" s="353"/>
     </row>
-    <row r="10" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A10" s="351" t="s">
         <v>23</v>
       </c>
@@ -34757,7 +34767,7 @@
       <c r="P10" s="353"/>
       <c r="Q10" s="353"/>
     </row>
-    <row r="11" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A11" s="351" t="s">
         <v>23</v>
       </c>
@@ -34780,7 +34790,7 @@
       <c r="P11" s="353"/>
       <c r="Q11" s="353"/>
     </row>
-    <row r="12" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A12" s="351" t="s">
         <v>23</v>
       </c>
@@ -34813,7 +34823,7 @@
       <c r="P12" s="353"/>
       <c r="Q12" s="353"/>
     </row>
-    <row r="13" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A13" s="351" t="s">
         <v>23</v>
       </c>
@@ -34846,7 +34856,7 @@
       <c r="P13" s="353"/>
       <c r="Q13" s="353"/>
     </row>
-    <row r="14" spans="1:17" s="253" customFormat="1" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A14" s="351" t="s">
         <v>23</v>
       </c>
@@ -34869,7 +34879,7 @@
       <c r="P14" s="353"/>
       <c r="Q14" s="353"/>
     </row>
-    <row r="15" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A15" s="351" t="s">
         <v>23</v>
       </c>
@@ -34904,7 +34914,7 @@
       <c r="P15" s="353"/>
       <c r="Q15" s="353"/>
     </row>
-    <row r="16" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A16" s="351" t="s">
         <v>23</v>
       </c>
@@ -34937,7 +34947,7 @@
       <c r="P16" s="353"/>
       <c r="Q16" s="353"/>
     </row>
-    <row r="17" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A17" s="351" t="s">
         <v>23</v>
       </c>
@@ -34972,7 +34982,7 @@
       <c r="P17" s="353"/>
       <c r="Q17" s="353"/>
     </row>
-    <row r="18" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A18" s="351" t="s">
         <v>23</v>
       </c>
@@ -35005,7 +35015,7 @@
       <c r="P18" s="353"/>
       <c r="Q18" s="353"/>
     </row>
-    <row r="19" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A19" s="351" t="s">
         <v>23</v>
       </c>
@@ -35038,7 +35048,7 @@
       <c r="P19" s="353"/>
       <c r="Q19" s="353"/>
     </row>
-    <row r="20" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A20" s="351" t="s">
         <v>23</v>
       </c>
@@ -35061,7 +35071,7 @@
       <c r="P20" s="353"/>
       <c r="Q20" s="353"/>
     </row>
-    <row r="21" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A21" s="351" t="s">
         <v>23</v>
       </c>
@@ -35092,7 +35102,7 @@
       <c r="P21" s="353"/>
       <c r="Q21" s="353"/>
     </row>
-    <row r="22" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A22" s="351" t="s">
         <v>23</v>
       </c>
@@ -35115,7 +35125,7 @@
       <c r="P22" s="353"/>
       <c r="Q22" s="353"/>
     </row>
-    <row r="23" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A23" s="351" t="s">
         <v>23</v>
       </c>
@@ -35146,7 +35156,7 @@
       <c r="P23" s="353"/>
       <c r="Q23" s="353"/>
     </row>
-    <row r="24" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A24" s="351" t="s">
         <v>23</v>
       </c>
@@ -35177,7 +35187,7 @@
       <c r="P24" s="353"/>
       <c r="Q24" s="353"/>
     </row>
-    <row r="25" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A25" s="351" t="s">
         <v>23</v>
       </c>
@@ -35208,7 +35218,7 @@
       <c r="P25" s="353"/>
       <c r="Q25" s="353"/>
     </row>
-    <row r="26" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A26" s="351" t="s">
         <v>23</v>
       </c>
@@ -35239,7 +35249,7 @@
       <c r="P26" s="353"/>
       <c r="Q26" s="353"/>
     </row>
-    <row r="27" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A27" s="351" t="s">
         <v>27</v>
       </c>
@@ -35268,7 +35278,7 @@
       <c r="P27" s="353"/>
       <c r="Q27" s="353"/>
     </row>
-    <row r="28" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A28" s="351" t="s">
         <v>29</v>
       </c>
@@ -35303,7 +35313,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A29" s="351" t="s">
         <v>29</v>
       </c>
@@ -35338,7 +35348,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A30" s="351" t="s">
         <v>29</v>
       </c>
@@ -35373,7 +35383,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A31" s="351" t="s">
         <v>29</v>
       </c>
@@ -35418,7 +35428,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A32" s="351" t="s">
         <v>31</v>
       </c>
@@ -35447,7 +35457,7 @@
       <c r="P32" s="353"/>
       <c r="Q32" s="353"/>
     </row>
-    <row r="33" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A33" s="351" t="s">
         <v>33</v>
       </c>
@@ -35488,7 +35498,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A34" s="351" t="s">
         <v>45</v>
       </c>
@@ -35517,7 +35527,7 @@
       <c r="P34" s="353"/>
       <c r="Q34" s="353"/>
     </row>
-    <row r="35" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A35" s="351" t="s">
         <v>45</v>
       </c>
@@ -35546,7 +35556,7 @@
       <c r="P35" s="353"/>
       <c r="Q35" s="353"/>
     </row>
-    <row r="36" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A36" s="351" t="s">
         <v>45</v>
       </c>
@@ -35575,7 +35585,7 @@
       <c r="P36" s="353"/>
       <c r="Q36" s="353"/>
     </row>
-    <row r="37" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A37" s="351" t="s">
         <v>45</v>
       </c>
@@ -35604,7 +35614,7 @@
       <c r="P37" s="353"/>
       <c r="Q37" s="353"/>
     </row>
-    <row r="38" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A38" s="351" t="s">
         <v>45</v>
       </c>
@@ -35633,7 +35643,7 @@
       <c r="P38" s="353"/>
       <c r="Q38" s="353"/>
     </row>
-    <row r="39" spans="1:17" s="253" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:17" s="253" customFormat="1" ht="17">
       <c r="A39" s="351" t="s">
         <v>45</v>
       </c>
@@ -35662,7 +35672,7 @@
       <c r="P39" s="353"/>
       <c r="Q39" s="353"/>
     </row>
-    <row r="40" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:17" ht="17">
       <c r="A40" s="351" t="s">
         <v>49</v>
       </c>
@@ -35691,7 +35701,7 @@
       <c r="P40" s="354"/>
       <c r="Q40" s="354"/>
     </row>
-    <row r="41" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:17" ht="17">
       <c r="A41" s="351" t="s">
         <v>49</v>
       </c>
@@ -35720,7 +35730,7 @@
       <c r="P41" s="354"/>
       <c r="Q41" s="354"/>
     </row>
-    <row r="42" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:17" ht="17">
       <c r="A42" s="351" t="s">
         <v>49</v>
       </c>
@@ -35749,7 +35759,7 @@
       <c r="P42" s="354"/>
       <c r="Q42" s="354"/>
     </row>
-    <row r="43" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:17" ht="17">
       <c r="A43" s="351" t="s">
         <v>49</v>
       </c>
@@ -35778,7 +35788,7 @@
       <c r="P43" s="354"/>
       <c r="Q43" s="354"/>
     </row>
-    <row r="44" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:17" ht="17">
       <c r="A44" s="351" t="s">
         <v>54</v>
       </c>
@@ -35807,7 +35817,7 @@
       <c r="P44" s="354"/>
       <c r="Q44" s="354"/>
     </row>
-    <row r="45" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:17" ht="17">
       <c r="A45" s="351" t="s">
         <v>57</v>
       </c>
@@ -35836,7 +35846,7 @@
       <c r="P45" s="353"/>
       <c r="Q45" s="353"/>
     </row>
-    <row r="46" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:17" ht="17">
       <c r="A46" s="351" t="s">
         <v>57</v>
       </c>
@@ -35865,7 +35875,7 @@
       <c r="P46" s="353"/>
       <c r="Q46" s="353"/>
     </row>
-    <row r="47" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:17" ht="17">
       <c r="A47" s="351" t="s">
         <v>57</v>
       </c>
@@ -35894,7 +35904,7 @@
       <c r="P47" s="353"/>
       <c r="Q47" s="353"/>
     </row>
-    <row r="48" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:17" ht="17">
       <c r="A48" s="351" t="s">
         <v>68</v>
       </c>
@@ -35923,7 +35933,7 @@
       <c r="P48" s="353"/>
       <c r="Q48" s="353"/>
     </row>
-    <row r="49" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:17" ht="17">
       <c r="A49" s="351" t="s">
         <v>68</v>
       </c>
@@ -35952,7 +35962,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:17" ht="17">
       <c r="A50" s="351" t="s">
         <v>68</v>
       </c>
@@ -35981,7 +35991,7 @@
       <c r="P50" s="353"/>
       <c r="Q50" s="353"/>
     </row>
-    <row r="51" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:17" ht="17">
       <c r="A51" s="351" t="s">
         <v>68</v>
       </c>
@@ -36004,7 +36014,7 @@
       <c r="P51" s="353"/>
       <c r="Q51" s="353"/>
     </row>
-    <row r="52" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:17" ht="17">
       <c r="A52" s="351" t="s">
         <v>70</v>
       </c>
@@ -36033,7 +36043,7 @@
       <c r="P52" s="353"/>
       <c r="Q52" s="353"/>
     </row>
-    <row r="53" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:17" ht="34">
       <c r="A53" s="351" t="s">
         <v>82</v>
       </c>
@@ -36058,7 +36068,7 @@
       <c r="P53" s="353"/>
       <c r="Q53" s="353"/>
     </row>
-    <row r="54" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:17" ht="17">
       <c r="A54" s="351" t="s">
         <v>82</v>
       </c>
@@ -36087,7 +36097,7 @@
       <c r="P54" s="353"/>
       <c r="Q54" s="353"/>
     </row>
-    <row r="55" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:17" ht="17">
       <c r="A55" s="351" t="s">
         <v>82</v>
       </c>
@@ -36116,7 +36126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:17" ht="17">
       <c r="A56" s="351" t="s">
         <v>82</v>
       </c>
@@ -36145,7 +36155,7 @@
       <c r="P56" s="353"/>
       <c r="Q56" s="353"/>
     </row>
-    <row r="57" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:17" ht="17">
       <c r="A57" s="351" t="s">
         <v>82</v>
       </c>
@@ -36174,7 +36184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:17" ht="17">
       <c r="A58" s="351" t="s">
         <v>112</v>
       </c>
@@ -36203,7 +36213,7 @@
       <c r="P58" s="353"/>
       <c r="Q58" s="353"/>
     </row>
-    <row r="59" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:17" ht="17">
       <c r="A59" s="351" t="s">
         <v>112</v>
       </c>
@@ -36232,7 +36242,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:17" ht="17">
       <c r="A60" s="351" t="s">
         <v>112</v>
       </c>
@@ -36255,7 +36265,7 @@
       <c r="P60" s="353"/>
       <c r="Q60" s="353"/>
     </row>
-    <row r="61" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:17" ht="17">
       <c r="A61" s="351" t="s">
         <v>85</v>
       </c>
@@ -36290,7 +36300,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:17" ht="17">
       <c r="A62" s="351" t="s">
         <v>85</v>
       </c>
@@ -36321,7 +36331,7 @@
       </c>
       <c r="Q62" s="353"/>
     </row>
-    <row r="63" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:17" ht="17">
       <c r="A63" s="351" t="s">
         <v>85</v>
       </c>
@@ -36350,7 +36360,7 @@
       <c r="P63" s="353"/>
       <c r="Q63" s="353"/>
     </row>
-    <row r="64" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:17" ht="17">
       <c r="A64" s="351" t="s">
         <v>85</v>
       </c>
@@ -36383,7 +36393,7 @@
       <c r="P64" s="353"/>
       <c r="Q64" s="353"/>
     </row>
-    <row r="65" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:17" ht="17">
       <c r="A65" s="351" t="s">
         <v>85</v>
       </c>
@@ -36418,7 +36428,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:17" ht="17">
       <c r="A66" s="351" t="s">
         <v>85</v>
       </c>
@@ -36445,7 +36455,7 @@
       <c r="P66" s="353"/>
       <c r="Q66" s="353"/>
     </row>
-    <row r="67" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:17" ht="17">
       <c r="A67" s="351" t="s">
         <v>85</v>
       </c>
@@ -36480,7 +36490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:17" ht="17">
       <c r="A68" s="351" t="s">
         <v>85</v>
       </c>
@@ -36515,7 +36525,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:17" ht="17">
       <c r="A69" s="351" t="s">
         <v>85</v>
       </c>
@@ -36544,7 +36554,7 @@
       <c r="P69" s="353"/>
       <c r="Q69" s="353"/>
     </row>
-    <row r="70" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:17" ht="17">
       <c r="A70" s="351" t="s">
         <v>85</v>
       </c>
@@ -36579,7 +36589,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:17" ht="17">
       <c r="A71" s="351" t="s">
         <v>85</v>
       </c>
@@ -36614,7 +36624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:17" ht="17">
       <c r="A72" s="351" t="s">
         <v>85</v>
       </c>
@@ -36641,7 +36651,7 @@
       <c r="P72" s="353"/>
       <c r="Q72" s="353"/>
     </row>
-    <row r="73" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:17" ht="17">
       <c r="A73" s="351" t="s">
         <v>85</v>
       </c>
@@ -36676,7 +36686,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:17" ht="17">
       <c r="A74" s="351" t="s">
         <v>85</v>
       </c>
@@ -36709,7 +36719,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:17" ht="17">
       <c r="A75" s="351" t="s">
         <v>85</v>
       </c>
@@ -36744,7 +36754,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:17" ht="34">
       <c r="A76" s="351" t="s">
         <v>87</v>
       </c>
@@ -36777,7 +36787,7 @@
       <c r="P76" s="353"/>
       <c r="Q76" s="353"/>
     </row>
-    <row r="77" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:17" ht="17">
       <c r="A77" s="351" t="s">
         <v>87</v>
       </c>
@@ -36812,7 +36822,7 @@
       <c r="P77" s="353"/>
       <c r="Q77" s="353"/>
     </row>
-    <row r="78" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:17" ht="17">
       <c r="A78" s="351" t="s">
         <v>87</v>
       </c>
@@ -36843,7 +36853,7 @@
       <c r="P78" s="353"/>
       <c r="Q78" s="353"/>
     </row>
-    <row r="79" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:17" ht="17">
       <c r="A79" s="351" t="s">
         <v>87</v>
       </c>
@@ -36878,7 +36888,7 @@
       <c r="P79" s="353"/>
       <c r="Q79" s="353"/>
     </row>
-    <row r="80" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:17" ht="17">
       <c r="A80" s="351" t="s">
         <v>88</v>
       </c>
@@ -36907,7 +36917,7 @@
       <c r="P80" s="353"/>
       <c r="Q80" s="353"/>
     </row>
-    <row r="81" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:17" ht="17">
       <c r="A81" s="351" t="s">
         <v>88</v>
       </c>
@@ -36936,7 +36946,7 @@
       <c r="P81" s="353"/>
       <c r="Q81" s="353"/>
     </row>
-    <row r="82" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:17" ht="17">
       <c r="A82" s="351" t="s">
         <v>88</v>
       </c>
@@ -36965,7 +36975,7 @@
       <c r="P82" s="353"/>
       <c r="Q82" s="353"/>
     </row>
-    <row r="83" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:17" ht="17">
       <c r="A83" s="351" t="s">
         <v>88</v>
       </c>
@@ -36994,7 +37004,7 @@
       <c r="P83" s="356"/>
       <c r="Q83" s="356"/>
     </row>
-    <row r="84" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:17" ht="17">
       <c r="A84" s="351" t="s">
         <v>88</v>
       </c>
@@ -37017,7 +37027,7 @@
       <c r="P84" s="353"/>
       <c r="Q84" s="353"/>
     </row>
-    <row r="85" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:17" ht="17">
       <c r="A85" s="351" t="s">
         <v>88</v>
       </c>
@@ -37046,7 +37056,7 @@
       <c r="P85" s="353"/>
       <c r="Q85" s="353"/>
     </row>
-    <row r="86" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:17" ht="17">
       <c r="A86" s="351" t="s">
         <v>88</v>
       </c>
@@ -37075,7 +37085,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:17" ht="17">
       <c r="A87" s="351" t="s">
         <v>88</v>
       </c>
@@ -37110,7 +37120,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:17" ht="17">
       <c r="A88" s="351" t="s">
         <v>88</v>
       </c>
@@ -37139,7 +37149,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:17" ht="17">
       <c r="A89" s="351" t="s">
         <v>88</v>
       </c>
@@ -37168,7 +37178,7 @@
       <c r="P89" s="357"/>
       <c r="Q89" s="357"/>
     </row>
-    <row r="90" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:17" ht="17">
       <c r="A90" s="351" t="s">
         <v>88</v>
       </c>
@@ -37197,7 +37207,7 @@
       <c r="P90" s="353"/>
       <c r="Q90" s="353"/>
     </row>
-    <row r="91" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:17" ht="17">
       <c r="A91" s="351" t="s">
         <v>88</v>
       </c>
@@ -37232,7 +37242,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:17" ht="17">
       <c r="A92" s="351" t="s">
         <v>88</v>
       </c>
@@ -37261,7 +37271,7 @@
       <c r="P92" s="353"/>
       <c r="Q92" s="353"/>
     </row>
-    <row r="93" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:17" ht="17">
       <c r="A93" s="351" t="s">
         <v>88</v>
       </c>
@@ -37290,7 +37300,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:17" ht="17">
       <c r="A94" s="351" t="s">
         <v>88</v>
       </c>
@@ -37319,7 +37329,7 @@
       <c r="P94" s="353"/>
       <c r="Q94" s="353"/>
     </row>
-    <row r="95" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:17" ht="17">
       <c r="A95" s="351" t="s">
         <v>88</v>
       </c>
@@ -37348,7 +37358,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:17" ht="17">
       <c r="A96" s="351" t="s">
         <v>88</v>
       </c>
@@ -37377,7 +37387,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:17" ht="17">
       <c r="A97" s="351" t="s">
         <v>88</v>
       </c>
@@ -37407,7 +37417,7 @@
       <c r="Q97" s="356"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:Q97"/>
+  <autoFilter ref="A7:Q97" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <mergeCells count="9">
     <mergeCell ref="B1:Q1"/>
     <mergeCell ref="B2:Q2"/>
@@ -37430,35 +37440,35 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:V35"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.75" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="14" style="275" customWidth="1"/>
-    <col min="2" max="2" width="11.1328125" style="275" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="275" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.33203125" style="275" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="275"/>
-    <col min="5" max="5" width="11.1328125" style="275" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" style="275" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.6640625" style="275" customWidth="1"/>
     <col min="7" max="7" width="8.6640625" style="275"/>
-    <col min="8" max="8" width="11.1328125" style="275" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1640625" style="275" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.6640625" style="275" customWidth="1"/>
     <col min="10" max="10" width="8.6640625" style="275"/>
-    <col min="11" max="11" width="11.1328125" style="275" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.86328125" style="275" customWidth="1"/>
+    <col min="11" max="11" width="11.1640625" style="275" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" style="275" customWidth="1"/>
     <col min="13" max="13" width="8.6640625" style="275"/>
-    <col min="14" max="14" width="12.86328125" style="275" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" style="275" customWidth="1"/>
     <col min="15" max="15" width="13.33203125" style="275" customWidth="1"/>
     <col min="16" max="16" width="8.6640625" style="275"/>
     <col min="17" max="17" width="12.33203125" style="275" customWidth="1"/>
     <col min="18" max="18" width="14.33203125" style="275" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8.6640625" style="275"/>
-    <col min="20" max="20" width="12.86328125" style="275" customWidth="1"/>
-    <col min="21" max="21" width="12.46484375" style="275" customWidth="1"/>
+    <col min="20" max="20" width="12.83203125" style="275" customWidth="1"/>
+    <col min="21" max="21" width="12.5" style="275" customWidth="1"/>
     <col min="22" max="16384" width="8.6640625" style="275"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22" ht="28.5" customHeight="1">
       <c r="A1" s="406" t="s">
         <v>380</v>
       </c>
@@ -37484,7 +37494,7 @@
       <c r="U1" s="406"/>
       <c r="V1" s="406"/>
     </row>
-    <row r="2" spans="1:22" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:22" ht="45.75" customHeight="1">
       <c r="A2" s="261"/>
       <c r="B2" s="407" t="s">
         <v>243</v>
@@ -37522,7 +37532,7 @@
       <c r="U2" s="407"/>
       <c r="V2" s="407"/>
     </row>
-    <row r="3" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:22" ht="31.5" customHeight="1">
       <c r="A3" s="262" t="s">
         <v>7</v>
       </c>
@@ -37590,7 +37600,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:22" ht="15" customHeight="1">
       <c r="A4" s="265" t="s">
         <v>260</v>
       </c>
@@ -37658,7 +37668,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:22" ht="15" customHeight="1">
       <c r="A5" s="265" t="s">
         <v>22</v>
       </c>
@@ -37728,7 +37738,7 @@
         <v>0.87181095775826023</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:22" ht="15" customHeight="1">
       <c r="A6" s="265" t="s">
         <v>23</v>
       </c>
@@ -37798,7 +37808,7 @@
         <v>0.21359072880515612</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:22" ht="15" customHeight="1">
       <c r="A7" s="265" t="s">
         <v>24</v>
       </c>
@@ -37868,7 +37878,7 @@
         <v>2.0806874263003885</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:22" ht="15" customHeight="1">
       <c r="A8" s="265" t="s">
         <v>103</v>
       </c>
@@ -37938,7 +37948,7 @@
         <v>0.97316722568279812</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:22" ht="15" customHeight="1">
       <c r="A9" s="265" t="s">
         <v>27</v>
       </c>
@@ -38007,7 +38017,7 @@
         <v>4.5610278372591011E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:22" ht="15" customHeight="1">
       <c r="A10" s="265" t="s">
         <v>29</v>
       </c>
@@ -38077,7 +38087,7 @@
         <v>0.71488971397401935</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:22" ht="15" customHeight="1">
       <c r="A11" s="265" t="s">
         <v>31</v>
       </c>
@@ -38147,7 +38157,7 @@
         <v>0.71413310343535052</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:22" ht="15" customHeight="1">
       <c r="A12" s="265" t="s">
         <v>33</v>
       </c>
@@ -38217,7 +38227,7 @@
         <v>0.52910677093278491</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:22" ht="15" customHeight="1">
       <c r="A13" s="265" t="s">
         <v>42</v>
       </c>
@@ -38287,7 +38297,7 @@
         <v>0.12081585656715191</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:22" ht="15" customHeight="1">
       <c r="A14" s="265" t="s">
         <v>45</v>
       </c>
@@ -38357,7 +38367,7 @@
         <v>0.91427615933412598</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:22" ht="15" customHeight="1">
       <c r="A15" s="265" t="s">
         <v>49</v>
       </c>
@@ -38427,7 +38437,7 @@
         <v>0.76753121998078766</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:22" ht="15" customHeight="1">
       <c r="A16" s="265" t="s">
         <v>54</v>
       </c>
@@ -38497,7 +38507,7 @@
         <v>0.67971234960586357</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:22" ht="15" customHeight="1">
       <c r="A17" s="265" t="s">
         <v>57</v>
       </c>
@@ -38567,7 +38577,7 @@
         <v>0.80464311989959614</v>
       </c>
     </row>
-    <row r="18" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:22" ht="15" customHeight="1">
       <c r="A18" s="265" t="s">
         <v>68</v>
       </c>
@@ -38637,7 +38647,7 @@
         <v>0.38118569380513556</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:22" ht="15" customHeight="1">
       <c r="A19" s="265" t="s">
         <v>378</v>
       </c>
@@ -38663,7 +38673,7 @@
       <c r="U19" s="271"/>
       <c r="V19" s="272"/>
     </row>
-    <row r="20" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:22" ht="15" customHeight="1">
       <c r="A20" s="265" t="s">
         <v>70</v>
       </c>
@@ -38733,7 +38743,7 @@
         <v>0.93996247654784248</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:22" ht="15" customHeight="1">
       <c r="A21" s="265" t="s">
         <v>102</v>
       </c>
@@ -38802,7 +38812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:22" ht="15" customHeight="1">
       <c r="A22" s="265" t="s">
         <v>71</v>
       </c>
@@ -38871,7 +38881,7 @@
         <v>0.81304601048340142</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:22" ht="15" customHeight="1">
       <c r="A23" s="265" t="s">
         <v>72</v>
       </c>
@@ -38941,7 +38951,7 @@
         <v>0.83553299492385791</v>
       </c>
     </row>
-    <row r="24" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:22" ht="15" customHeight="1">
       <c r="A24" s="265" t="s">
         <v>73</v>
       </c>
@@ -39011,7 +39021,7 @@
         <v>0.76678445229681969</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:22" ht="15" customHeight="1">
       <c r="A25" s="265" t="s">
         <v>76</v>
       </c>
@@ -39081,7 +39091,7 @@
         <v>0.99971234058874292</v>
       </c>
     </row>
-    <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:22" ht="15" customHeight="1">
       <c r="A26" s="265" t="s">
         <v>82</v>
       </c>
@@ -39151,7 +39161,7 @@
         <v>0.14988847108109765</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:22" ht="15" customHeight="1">
       <c r="A27" s="265" t="s">
         <v>112</v>
       </c>
@@ -39221,7 +39231,7 @@
         <v>0.63795480692386741</v>
       </c>
     </row>
-    <row r="28" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:22" ht="15" customHeight="1">
       <c r="A28" s="265" t="s">
         <v>85</v>
       </c>
@@ -39291,7 +39301,7 @@
         <v>0.7758207934336524</v>
       </c>
     </row>
-    <row r="29" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:22" ht="15" customHeight="1">
       <c r="A29" s="265" t="s">
         <v>86</v>
       </c>
@@ -39361,7 +39371,7 @@
         <v>0.24256651016455191</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:22" ht="15" customHeight="1">
       <c r="A30" s="265" t="s">
         <v>87</v>
       </c>
@@ -39431,7 +39441,7 @@
         <v>0.89303222508770708</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:22" ht="15" customHeight="1">
       <c r="A31" s="265" t="s">
         <v>88</v>
       </c>
@@ -39501,7 +39511,7 @@
         <v>1.0671848408646398</v>
       </c>
     </row>
-    <row r="32" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:22" ht="15" customHeight="1">
       <c r="A32" s="265" t="s">
         <v>118</v>
       </c>
@@ -39590,9 +39600,9 @@
         <v>0.45816863493993965</v>
       </c>
     </row>
-    <row r="35" ht="21" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="35" ht="21" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A3:V32"/>
+  <autoFilter ref="A3:V32" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <mergeCells count="8">
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="E2:G2"/>
@@ -39611,4 +39621,10 @@
 Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{3de9faa6-9fe1-49b3-9a08-227a296b54a6}" enabled="1" method="Privileged" siteId="{66d73691-ea97-48b1-95d5-e94f0a46b878}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>